--- a/AAII_Financials/Quarterly/AKA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AKA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="92">
   <si>
     <t>AKA</t>
   </si>
@@ -656,263 +656,275 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>148900</v>
+      </c>
+      <c r="E8" s="3">
         <v>140800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>136000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>120500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>149100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>155800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>158500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>148300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>182400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>161800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>149200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>68800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>70800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>63300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>46800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>35000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>33800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>30300</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>72500</v>
+      </c>
+      <c r="E9" s="3">
         <v>62900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>58700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>52000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>70400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>69000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>71000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>64100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>82900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>75700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>67800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>28200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>28100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>24800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>20800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>15800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>14700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>14200</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>76400</v>
+      </c>
+      <c r="E10" s="3">
         <v>77900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>77300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>68500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>78700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>86800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>87500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>84200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>99500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>86100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>81400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>40600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>42700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>38500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>26000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>19200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>19100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>16100</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -933,8 +945,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -989,8 +1002,11 @@
       <c r="T12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,41 +1061,44 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>68500</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
         <v>173800</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>10900</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1092,8 +1111,8 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1101,41 +1120,44 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2900</v>
+        <v>2700</v>
       </c>
       <c r="E15" s="3">
         <v>2900</v>
       </c>
       <c r="F15" s="3">
+        <v>2900</v>
+      </c>
+      <c r="G15" s="3">
         <v>3000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3700</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1148,8 +1170,8 @@
       <c r="Q15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="R15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1157,8 +1179,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1201,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>154300</v>
+      </c>
+      <c r="E17" s="3">
         <v>211200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>137100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>127000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>324700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>153100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>161000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>145000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>177200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>171500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>141900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>66100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>62900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>52400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>43300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>35000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>34200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>29100</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-70400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-6500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-175600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-9700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>7300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>10900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3500</v>
       </c>
-      <c r="R18" s="3">
-        <v>0</v>
-      </c>
       <c r="S18" s="3">
+        <v>0</v>
+      </c>
+      <c r="T18" s="3">
         <v>-400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,153 +1342,160 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-600</v>
       </c>
       <c r="L20" s="3">
         <v>-600</v>
       </c>
       <c r="M20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="N20" s="3">
         <v>-4100</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-100</v>
       </c>
       <c r="O20" s="3">
         <v>-100</v>
       </c>
       <c r="P20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-200</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-100</v>
       </c>
       <c r="R20" s="3">
         <v>-100</v>
       </c>
       <c r="S20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-66400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-170100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>10000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-6100</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="3">
         <v>14500</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3">
         <v>6400</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="E22" s="3">
         <v>2800</v>
       </c>
       <c r="F22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G22" s="3">
         <v>2900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>4100</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
@@ -1469,8 +1508,8 @@
       <c r="Q22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="R22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1478,120 +1517,129 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-73700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-177600</v>
       </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
       <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
         <v>-5200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-14400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>10700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E24" s="3">
         <v>-3300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-3700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-4300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1100</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>-100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1694,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-70400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-173900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1500</v>
       </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
       <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
         <v>-10100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-70400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-173900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1500</v>
       </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
       <c r="L27" s="3">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3">
         <v>-9900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>7100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1871,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1930,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1989,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,120 +2048,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
         <v>500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>600</v>
       </c>
       <c r="L32" s="3">
         <v>600</v>
       </c>
       <c r="M32" s="3">
+        <v>600</v>
+      </c>
+      <c r="N32" s="3">
         <v>4100</v>
-      </c>
-      <c r="N32" s="3">
-        <v>100</v>
       </c>
       <c r="O32" s="3">
         <v>100</v>
       </c>
       <c r="P32" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q32" s="3">
         <v>200</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>100</v>
       </c>
       <c r="R32" s="3">
         <v>100</v>
       </c>
       <c r="S32" s="3">
+        <v>100</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-70400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-173900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1500</v>
       </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
       <c r="L33" s="3">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3">
         <v>-9900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>7100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2225,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-70400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-173900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1500</v>
       </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
       <c r="L35" s="3">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3">
         <v>-9900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>7100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2373,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,44 +2396,45 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E41" s="3">
         <v>20700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>25900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>30200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>46300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>31100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>29100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>41200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>38800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>54400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>34300</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2367,8 +2453,11 @@
       <c r="T41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2423,44 +2512,47 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E43" s="3">
         <v>3300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6900</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>8</v>
       </c>
@@ -2479,44 +2571,47 @@
       <c r="T43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E44" s="3">
         <v>100000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>106700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>112500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>126500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>136900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>143900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>120600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>115800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>95800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>99700</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>8</v>
       </c>
@@ -2535,44 +2630,47 @@
       <c r="T44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E45" s="3">
         <v>30200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>25800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>22700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>21500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>28500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>32800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>31700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>27100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>22400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>15500</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
@@ -2591,44 +2689,47 @@
       <c r="T45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>135700</v>
+      </c>
+      <c r="E46" s="3">
         <v>154200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>161000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>168700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>197600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>200400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>208800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>197000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>184300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>176600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>156400</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>8</v>
       </c>
@@ -2647,8 +2748,11 @@
       <c r="T46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2703,44 +2807,47 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>64600</v>
+      </c>
+      <c r="E48" s="3">
         <v>65000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>67600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>66800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>66300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>64000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>57400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>59800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>41100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>39100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>38900</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>8</v>
       </c>
@@ -2759,44 +2866,47 @@
       <c r="T48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>159200</v>
+      </c>
+      <c r="E49" s="3">
         <v>157600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>233800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>238200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>243800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>404900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>431900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>469800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>461600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>418700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>439800</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>8</v>
       </c>
@@ -2815,8 +2925,11 @@
       <c r="T49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2984,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,13 +3043,16 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1700</v>
+        <v>2200</v>
       </c>
       <c r="E52" s="3">
         <v>1700</v>
@@ -2942,29 +3061,29 @@
         <v>1700</v>
       </c>
       <c r="G52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H52" s="3">
         <v>1900</v>
-      </c>
-      <c r="H52" s="3">
-        <v>900</v>
       </c>
       <c r="I52" s="3">
         <v>900</v>
       </c>
       <c r="J52" s="3">
+        <v>900</v>
+      </c>
+      <c r="K52" s="3">
         <v>1000</v>
-      </c>
-      <c r="K52" s="3">
-        <v>900</v>
       </c>
       <c r="L52" s="3">
         <v>900</v>
       </c>
       <c r="M52" s="3">
+        <v>900</v>
+      </c>
+      <c r="N52" s="3">
         <v>1000</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>8</v>
       </c>
@@ -2983,8 +3102,11 @@
       <c r="T52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,44 +3161,47 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>361700</v>
+      </c>
+      <c r="E54" s="3">
         <v>378400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>464200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>475500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>509600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>670300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>699100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>727600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>687800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>635200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>636100</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>8</v>
       </c>
@@ -3095,8 +3220,11 @@
       <c r="T54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3245,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,44 +3268,45 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E57" s="3">
         <v>27500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>20700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>16500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>20900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>33700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>28500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>17300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>25100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>22500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>19300</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>8</v>
       </c>
@@ -3195,22 +3325,25 @@
       <c r="T57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E58" s="3">
         <v>7700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6300</v>
-      </c>
-      <c r="G58" s="3">
-        <v>5600</v>
       </c>
       <c r="H58" s="3">
         <v>5600</v>
@@ -3225,14 +3358,14 @@
         <v>5600</v>
       </c>
       <c r="L58" s="3">
+        <v>5600</v>
+      </c>
+      <c r="M58" s="3">
         <v>5000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2900</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>8</v>
       </c>
@@ -3251,44 +3384,47 @@
       <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>54400</v>
+      </c>
+      <c r="E59" s="3">
         <v>53000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>54000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>52900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>61800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>69500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>74900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>67100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>77300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>60000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>48900</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>8</v>
       </c>
@@ -3307,44 +3443,47 @@
       <c r="T59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>86000</v>
+      </c>
+      <c r="E60" s="3">
         <v>88100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>81700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>75800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>88300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>108800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>108900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>90000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>108000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>87500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>71100</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>8</v>
       </c>
@@ -3363,44 +3502,47 @@
       <c r="T60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>90100</v>
+      </c>
+      <c r="E61" s="3">
         <v>99000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>113000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>126100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>138000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>124300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>125600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>126900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>103200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>93200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>154200</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3419,44 +3561,47 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E62" s="3">
         <v>37100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>39400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>38100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>36200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>37400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>38000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>42400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>25600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>45600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>52500</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>8</v>
       </c>
@@ -3475,8 +3620,11 @@
       <c r="T62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3679,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3738,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,44 +3797,47 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>213100</v>
+      </c>
+      <c r="E66" s="3">
         <v>224200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>234100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>240000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>262600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>270600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>272500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>259300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>236800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>226300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>426600</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>8</v>
       </c>
@@ -3699,8 +3856,11 @@
       <c r="T66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3881,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3938,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3997,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4056,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,44 +4115,47 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-267400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-253500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-183100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-178100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-168500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>8200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>8100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>18000</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>8</v>
       </c>
@@ -4001,8 +4174,11 @@
       <c r="T72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4233,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4292,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,44 +4351,47 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>148600</v>
+      </c>
+      <c r="E76" s="3">
         <v>154200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>230100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>235500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>247100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>399700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>426500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>468300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>451000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>408900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>209500</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>8</v>
       </c>
@@ -4225,8 +4410,11 @@
       <c r="T76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4469,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-70400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-173900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1500</v>
       </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
       <c r="L81" s="3">
+        <v>0</v>
+      </c>
+      <c r="M81" s="3">
         <v>-9900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>7100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,50 +4617,51 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E83" s="3">
         <v>4500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4200</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P83" s="3">
         <v>6800</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>8</v>
       </c>
@@ -4476,8 +4674,11 @@
       <c r="T83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4733,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4792,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4851,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4910,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,50 +4969,53 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E89" s="3">
         <v>10800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>10300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>11100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>12200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-8700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>13200</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P89" s="3">
         <v>21700</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>8</v>
       </c>
@@ -4812,8 +5028,11 @@
       <c r="T89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,50 +5053,51 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1800</v>
+        <v>-500</v>
       </c>
       <c r="E91" s="3">
         <v>-1800</v>
       </c>
       <c r="F91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="G91" s="3">
         <v>-1900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2000</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O91" s="3">
+      <c r="O91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P91" s="3">
         <v>-1300</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>8</v>
       </c>
@@ -4890,8 +5110,11 @@
       <c r="T91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5169,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,50 +5228,53 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1800</v>
+        <v>-500</v>
       </c>
       <c r="E94" s="3">
         <v>-1800</v>
       </c>
       <c r="F94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="G94" s="3">
         <v>-1900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-9100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-26300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-22700</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P94" s="3">
         <v>-2400</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>8</v>
       </c>
@@ -5058,8 +5287,11 @@
       <c r="T94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5312,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5136,8 +5369,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5428,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5487,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,50 +5546,53 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-14100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-12700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-11400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>13800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>22300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>8300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>30000</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P100" s="3">
         <v>1200</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>8</v>
       </c>
@@ -5360,50 +5605,53 @@
       <c r="T100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-100</v>
+        <v>1200</v>
       </c>
       <c r="E101" s="3">
         <v>-100</v>
       </c>
       <c r="F101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-400</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P101" s="3">
         <v>700</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>8</v>
       </c>
@@ -5416,50 +5664,53 @@
       <c r="T101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-16100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>15300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-12900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-15600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>20100</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P102" s="3">
         <v>21300</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>8</v>
       </c>
@@ -5470,6 +5721,9 @@
         <v>8</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AKA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AKA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
   <si>
     <t>AKA</t>
   </si>
@@ -656,275 +656,288 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>116800</v>
+      </c>
+      <c r="E8" s="3">
         <v>148900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>140800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>136000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>120500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>149100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>155800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>158500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>148300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>182400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>161800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>149200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>68800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>70800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>63300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>46800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>35000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>33800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>30300</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E9" s="3">
         <v>72500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>62900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>58700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>52000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>70400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>69000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>71000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>64100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>82900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>75700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>67800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>28200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>28100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>24800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>20800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>15800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>14700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>14200</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>65600</v>
+      </c>
+      <c r="E10" s="3">
         <v>76400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>77900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>77300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>68500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>78700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>86800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>87500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>84200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>99500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>86100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>81400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>40600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>42700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>38500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>26000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>19200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>19100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>16100</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -946,8 +959,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1005,8 +1019,11 @@
       <c r="U12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1064,44 +1081,47 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>68500</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>173800</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>10900</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1114,8 +1134,8 @@
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1123,44 +1143,47 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E15" s="3">
         <v>2700</v>
-      </c>
-      <c r="E15" s="3">
-        <v>2900</v>
       </c>
       <c r="F15" s="3">
         <v>2900</v>
       </c>
       <c r="G15" s="3">
+        <v>2900</v>
+      </c>
+      <c r="H15" s="3">
         <v>3000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3700</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1173,8 +1196,8 @@
       <c r="R15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
+      <c r="S15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
@@ -1182,8 +1205,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1202,126 +1228,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>122900</v>
+      </c>
+      <c r="E17" s="3">
         <v>154300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>211200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>137100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>127000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>324700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>153100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>161000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>145000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>177200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>171500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>141900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>66100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>62900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>52400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>43300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>35000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>34200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>29100</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-70400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-6500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-175600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-9700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>10900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3500</v>
       </c>
-      <c r="S18" s="3">
-        <v>0</v>
-      </c>
       <c r="T18" s="3">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3">
         <v>-400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1343,162 +1376,169 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-600</v>
       </c>
       <c r="M20" s="3">
         <v>-600</v>
       </c>
       <c r="N20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="O20" s="3">
         <v>-4100</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-100</v>
       </c>
       <c r="P20" s="3">
         <v>-100</v>
       </c>
       <c r="Q20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R20" s="3">
         <v>-200</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-100</v>
       </c>
       <c r="S20" s="3">
         <v>-100</v>
       </c>
       <c r="T20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-66400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-170100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>10000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-6100</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="3">
         <v>14500</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="3">
         <v>6400</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E22" s="3">
         <v>2700</v>
-      </c>
-      <c r="E22" s="3">
-        <v>2800</v>
       </c>
       <c r="F22" s="3">
         <v>2800</v>
       </c>
       <c r="G22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="H22" s="3">
         <v>2900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>4100</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>8</v>
       </c>
@@ -1511,8 +1551,8 @@
       <c r="R22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
@@ -1520,126 +1560,135 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-73700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-177600</v>
       </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
       <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
         <v>-5200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-14400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>10700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>5800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-3300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-3700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-4300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1100</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>-100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1697,126 +1746,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-13900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-70400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-173900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1500</v>
       </c>
-      <c r="L26" s="3">
-        <v>0</v>
-      </c>
       <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
         <v>-10100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>7300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-13900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-70400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-173900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1500</v>
       </c>
-      <c r="L27" s="3">
-        <v>0</v>
-      </c>
       <c r="M27" s="3">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3">
         <v>-9900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>7100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1874,8 +1932,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1933,8 +1994,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1992,8 +2056,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2051,126 +2118,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>500</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
-      </c>
-      <c r="L32" s="3">
-        <v>600</v>
       </c>
       <c r="M32" s="3">
         <v>600</v>
       </c>
       <c r="N32" s="3">
+        <v>600</v>
+      </c>
+      <c r="O32" s="3">
         <v>4100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>100</v>
       </c>
       <c r="P32" s="3">
         <v>100</v>
       </c>
       <c r="Q32" s="3">
+        <v>100</v>
+      </c>
+      <c r="R32" s="3">
         <v>200</v>
-      </c>
-      <c r="R32" s="3">
-        <v>100</v>
       </c>
       <c r="S32" s="3">
         <v>100</v>
       </c>
       <c r="T32" s="3">
+        <v>100</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-13900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-70400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-173900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1500</v>
       </c>
-      <c r="L33" s="3">
-        <v>0</v>
-      </c>
       <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
         <v>-9900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>7100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2228,131 +2304,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-13900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-70400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-173900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1500</v>
       </c>
-      <c r="L35" s="3">
-        <v>0</v>
-      </c>
       <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3">
         <v>-9900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>7100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2374,8 +2459,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2397,8 +2483,9 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2406,38 +2493,38 @@
         <v>21900</v>
       </c>
       <c r="E41" s="3">
+        <v>21900</v>
+      </c>
+      <c r="F41" s="3">
         <v>20700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>25900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>30200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>46300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>31100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>29100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>41200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>38800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>54400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>34300</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2456,8 +2543,11 @@
       <c r="U41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2515,47 +2605,50 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E43" s="3">
         <v>4800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6900</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>8</v>
       </c>
@@ -2574,47 +2667,50 @@
       <c r="U43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>91500</v>
+      </c>
+      <c r="E44" s="3">
         <v>91000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>100000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>106700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>112500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>126500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>136900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>143900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>120600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>115800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>95800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>99700</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
@@ -2633,47 +2729,50 @@
       <c r="U44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E45" s="3">
         <v>18000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>30200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>25800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>22700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>21500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>28500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>32800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>31700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>27100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>22400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>15500</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
@@ -2692,47 +2791,50 @@
       <c r="U45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>133600</v>
+      </c>
+      <c r="E46" s="3">
         <v>135700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>154200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>161000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>168700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>197600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>200400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>208800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>197000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>184300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>176600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>156400</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>8</v>
       </c>
@@ -2751,8 +2853,11 @@
       <c r="U46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2810,47 +2915,50 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>65200</v>
+      </c>
+      <c r="E48" s="3">
         <v>64600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>65000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>67600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>66800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>66300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>64000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>57400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>59800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>41100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>39100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>38900</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>8</v>
       </c>
@@ -2869,47 +2977,50 @@
       <c r="U48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>153100</v>
+      </c>
+      <c r="E49" s="3">
         <v>159200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>157600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>233800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>238200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>243800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>404900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>431900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>469800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>461600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>418700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>439800</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>8</v>
       </c>
@@ -2928,8 +3039,11 @@
       <c r="U49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2987,8 +3101,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3046,16 +3163,19 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E52" s="3">
         <v>2200</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1700</v>
       </c>
       <c r="F52" s="3">
         <v>1700</v>
@@ -3064,29 +3184,29 @@
         <v>1700</v>
       </c>
       <c r="H52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I52" s="3">
         <v>1900</v>
-      </c>
-      <c r="I52" s="3">
-        <v>900</v>
       </c>
       <c r="J52" s="3">
         <v>900</v>
       </c>
       <c r="K52" s="3">
+        <v>900</v>
+      </c>
+      <c r="L52" s="3">
         <v>1000</v>
-      </c>
-      <c r="L52" s="3">
-        <v>900</v>
       </c>
       <c r="M52" s="3">
         <v>900</v>
       </c>
       <c r="N52" s="3">
+        <v>900</v>
+      </c>
+      <c r="O52" s="3">
         <v>1000</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3105,8 +3225,11 @@
       <c r="U52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3164,47 +3287,50 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>355800</v>
+      </c>
+      <c r="E54" s="3">
         <v>361700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>378400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>464200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>475500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>509600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>670300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>699100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>727600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>687800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>635200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>636100</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>8</v>
       </c>
@@ -3223,8 +3349,11 @@
       <c r="U54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3246,8 +3375,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3269,47 +3399,48 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E57" s="3">
         <v>28300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>27500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>20700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>16500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>20900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>33700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>28500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>17300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>25100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>22500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>19300</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>8</v>
       </c>
@@ -3328,25 +3459,28 @@
       <c r="U57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E58" s="3">
         <v>3300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6300</v>
-      </c>
-      <c r="H58" s="3">
-        <v>5600</v>
       </c>
       <c r="I58" s="3">
         <v>5600</v>
@@ -3361,14 +3495,14 @@
         <v>5600</v>
       </c>
       <c r="M58" s="3">
+        <v>5600</v>
+      </c>
+      <c r="N58" s="3">
         <v>5000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2900</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
@@ -3387,47 +3521,50 @@
       <c r="U58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>54300</v>
+      </c>
+      <c r="E59" s="3">
         <v>54400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>53000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>54000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>52900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>61800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>69500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>74900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>67100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>77300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>60000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>48900</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>8</v>
       </c>
@@ -3446,47 +3583,50 @@
       <c r="U59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>82500</v>
+      </c>
+      <c r="E60" s="3">
         <v>86000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>88100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>81700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>75800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>88300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>108800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>108900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>90000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>108000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>87500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>71100</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>8</v>
       </c>
@@ -3505,47 +3645,50 @@
       <c r="U60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>98800</v>
+      </c>
+      <c r="E61" s="3">
         <v>90100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>99000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>113000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>126100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>138000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>124300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>125600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>126900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>103200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>93200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>154200</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3564,47 +3707,50 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>38900</v>
+      </c>
+      <c r="E62" s="3">
         <v>37000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>37100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>39400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>38100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>36200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>37400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>38000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>42400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>25600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>45600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>52500</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>8</v>
       </c>
@@ -3623,8 +3769,11 @@
       <c r="U62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3682,8 +3831,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3741,8 +3893,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3800,47 +3955,50 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>220200</v>
+      </c>
+      <c r="E66" s="3">
         <v>213100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>224200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>234100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>240000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>262600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>270600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>272500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>259300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>236800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>226300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>426600</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>8</v>
       </c>
@@ -3859,8 +4017,11 @@
       <c r="U66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3882,8 +4043,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3941,8 +4103,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4000,8 +4165,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4059,8 +4227,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4118,47 +4289,50 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-276300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-267400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-253500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-183100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-178100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-168500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>8200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>18000</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>8</v>
       </c>
@@ -4177,8 +4351,11 @@
       <c r="U72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4236,8 +4413,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4295,8 +4475,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4354,47 +4537,50 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>135500</v>
+      </c>
+      <c r="E76" s="3">
         <v>148600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>154200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>230100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>235500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>247100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>399700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>426500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>468300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>451000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>408900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>209500</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>8</v>
       </c>
@@ -4413,8 +4599,11 @@
       <c r="U76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4472,131 +4661,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-13900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-70400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-173900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1500</v>
       </c>
-      <c r="L81" s="3">
-        <v>0</v>
-      </c>
       <c r="M81" s="3">
+        <v>0</v>
+      </c>
+      <c r="N81" s="3">
         <v>-9900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>7100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4618,53 +4816,54 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E83" s="3">
         <v>4400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4200</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q83" s="3">
         <v>6800</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>8</v>
       </c>
@@ -4677,8 +4876,11 @@
       <c r="U83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4736,8 +4938,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4795,8 +5000,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4854,8 +5062,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4913,8 +5124,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4972,53 +5186,56 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E89" s="3">
         <v>15400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>10800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>10300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>11100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>12200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-8700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-14900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>13200</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q89" s="3">
         <v>21700</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>8</v>
       </c>
@@ -5031,8 +5248,11 @@
       <c r="U89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5054,53 +5274,54 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-500</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-1800</v>
       </c>
       <c r="F91" s="3">
         <v>-1800</v>
       </c>
       <c r="G91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="H91" s="3">
         <v>-1900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2000</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P91" s="3">
+      <c r="P91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>8</v>
       </c>
@@ -5113,8 +5334,11 @@
       <c r="U91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5172,8 +5396,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5231,53 +5458,56 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-500</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-1800</v>
       </c>
       <c r="F94" s="3">
         <v>-1800</v>
       </c>
       <c r="G94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="H94" s="3">
         <v>-1900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-9100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-26300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-22700</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>8</v>
       </c>
@@ -5290,8 +5520,11 @@
       <c r="U94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5313,8 +5546,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5372,8 +5606,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5431,8 +5668,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5490,8 +5730,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5549,53 +5792,56 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-14600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-14100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-12700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-11400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>13800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>22300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>8300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>30000</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q100" s="3">
         <v>1200</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>8</v>
       </c>
@@ -5608,53 +5854,56 @@
       <c r="U100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E101" s="3">
         <v>1200</v>
-      </c>
-      <c r="E101" s="3">
-        <v>-100</v>
       </c>
       <c r="F101" s="3">
         <v>-100</v>
       </c>
       <c r="G101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-400</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101" s="3">
         <v>700</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>8</v>
       </c>
@@ -5667,53 +5916,56 @@
       <c r="U101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E102" s="3">
         <v>1400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-16100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>15300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-12900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-15600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>20100</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P102" s="3">
+      <c r="P102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q102" s="3">
         <v>21300</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>8</v>
       </c>
@@ -5724,6 +5976,9 @@
         <v>8</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AKA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AKA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
   <si>
     <t>AKA</t>
   </si>
@@ -656,288 +656,301 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>148900</v>
+      </c>
+      <c r="E8" s="3">
         <v>116800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>148900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>140800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>136000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>120500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>149100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>155800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>158500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>148300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>182400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>161800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>149200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>68800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>70800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>63300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>46800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>35000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>33800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>30300</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E9" s="3">
         <v>51200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>72500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>62900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>58700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>52000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>70400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>69000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>71000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>64100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>82900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>75700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>67800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>28200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>28100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>24800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>20800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>15800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>14700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>14200</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>85900</v>
+      </c>
+      <c r="E10" s="3">
         <v>65600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>76400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>77900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>77300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>68500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>78700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>86800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>87500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>84200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>99500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>86100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>81400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>40600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>42700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>38500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>26000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>19200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>19100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>16100</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -960,8 +973,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1022,8 +1036,11 @@
       <c r="V12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,47 +1101,50 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>68500</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>173800</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>10900</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1137,8 +1157,8 @@
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1146,47 +1166,50 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E15" s="3">
         <v>2800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2700</v>
-      </c>
-      <c r="F15" s="3">
-        <v>2900</v>
       </c>
       <c r="G15" s="3">
         <v>2900</v>
       </c>
       <c r="H15" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I15" s="3">
         <v>3000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3700</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1199,8 +1222,8 @@
       <c r="S15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T15" s="3">
-        <v>0</v>
+      <c r="T15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
@@ -1208,8 +1231,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>148300</v>
+      </c>
+      <c r="E17" s="3">
         <v>122900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>154300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>211200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>137100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>127000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>324700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>153100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>161000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>145000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>177200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>171500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>141900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>66100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>62900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>52400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>43300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>35000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>34200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>29100</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-6100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-5400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-70400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-6500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-175600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-9700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>7900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>10900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3500</v>
       </c>
-      <c r="T18" s="3">
-        <v>0</v>
-      </c>
       <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
         <v>-400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,171 +1410,178 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-600</v>
       </c>
       <c r="N20" s="3">
         <v>-600</v>
       </c>
       <c r="O20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="P20" s="3">
         <v>-4100</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-100</v>
       </c>
       <c r="Q20" s="3">
         <v>-100</v>
       </c>
       <c r="R20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S20" s="3">
         <v>-200</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-100</v>
       </c>
       <c r="T20" s="3">
         <v>-100</v>
       </c>
       <c r="U20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-66400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-170100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>10000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-6100</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3">
         <v>14500</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T21" s="3">
         <v>6400</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E22" s="3">
         <v>2300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2700</v>
-      </c>
-      <c r="F22" s="3">
-        <v>2800</v>
       </c>
       <c r="G22" s="3">
         <v>2800</v>
       </c>
       <c r="H22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I22" s="3">
         <v>2900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>4100</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
@@ -1554,8 +1594,8 @@
       <c r="S22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -1563,132 +1603,141 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-73700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-10400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-177600</v>
       </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
       <c r="K23" s="3">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
         <v>-5200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-14400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>10700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>5800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-3300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-3700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-4300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1100</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>-100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-13900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-70400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-173900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1500</v>
       </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
       <c r="N26" s="3">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
         <v>-10100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>7300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-13900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-70400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-173900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1500</v>
       </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
       <c r="N27" s="3">
+        <v>0</v>
+      </c>
+      <c r="O27" s="3">
         <v>-9900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>7100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1997,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,132 +2188,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E32" s="3">
         <v>500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>600</v>
       </c>
       <c r="N32" s="3">
         <v>600</v>
       </c>
       <c r="O32" s="3">
+        <v>600</v>
+      </c>
+      <c r="P32" s="3">
         <v>4100</v>
-      </c>
-      <c r="P32" s="3">
-        <v>100</v>
       </c>
       <c r="Q32" s="3">
         <v>100</v>
       </c>
       <c r="R32" s="3">
+        <v>100</v>
+      </c>
+      <c r="S32" s="3">
         <v>200</v>
-      </c>
-      <c r="S32" s="3">
-        <v>100</v>
       </c>
       <c r="T32" s="3">
         <v>100</v>
       </c>
       <c r="U32" s="3">
+        <v>100</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-13900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-70400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-173900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1500</v>
       </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
       <c r="N33" s="3">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3">
         <v>-9900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>7100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-13900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-70400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-173900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1500</v>
       </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
       <c r="N35" s="3">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3">
         <v>-9900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>7100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,50 +2570,51 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>21900</v>
+        <v>25500</v>
       </c>
       <c r="E41" s="3">
         <v>21900</v>
       </c>
       <c r="F41" s="3">
+        <v>21900</v>
+      </c>
+      <c r="G41" s="3">
         <v>20700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>25900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>30200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>46300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>31100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>29100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>41200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>38800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>54400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>34300</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2546,8 +2633,11 @@
       <c r="V41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2608,50 +2698,53 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E43" s="3">
         <v>4100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6900</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>8</v>
       </c>
@@ -2670,50 +2763,53 @@
       <c r="V43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>106700</v>
+      </c>
+      <c r="E44" s="3">
         <v>91500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>91000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>100000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>106700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>112500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>126500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>136900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>143900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>120600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>115800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>95800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>99700</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>8</v>
       </c>
@@ -2732,50 +2828,53 @@
       <c r="V44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E45" s="3">
         <v>16100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>18000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>30200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>25800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>22700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>21500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>28500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>32800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>31700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>27100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>22400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>15500</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>8</v>
       </c>
@@ -2794,50 +2893,53 @@
       <c r="V45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>155100</v>
+      </c>
+      <c r="E46" s="3">
         <v>133600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>135700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>154200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>161000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>168700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>197600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>200400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>208800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>197000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>184300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>176600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>156400</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>8</v>
       </c>
@@ -2856,8 +2958,11 @@
       <c r="V46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2918,50 +3023,53 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>77800</v>
+      </c>
+      <c r="E48" s="3">
         <v>65200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>64600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>65000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>67600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>66800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>66300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>64000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>57400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>59800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>41100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>39100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>38900</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>8</v>
       </c>
@@ -2980,50 +3088,53 @@
       <c r="V48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>152100</v>
+      </c>
+      <c r="E49" s="3">
         <v>153100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>159200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>157600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>233800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>238200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>243800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>404900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>431900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>469800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>461600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>418700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>439800</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>8</v>
       </c>
@@ -3042,8 +3153,11 @@
       <c r="V49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,8 +3283,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3175,10 +3295,10 @@
         <v>3800</v>
       </c>
       <c r="E52" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F52" s="3">
         <v>2200</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1700</v>
       </c>
       <c r="G52" s="3">
         <v>1700</v>
@@ -3187,29 +3307,29 @@
         <v>1700</v>
       </c>
       <c r="I52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J52" s="3">
         <v>1900</v>
-      </c>
-      <c r="J52" s="3">
-        <v>900</v>
       </c>
       <c r="K52" s="3">
         <v>900</v>
       </c>
       <c r="L52" s="3">
+        <v>900</v>
+      </c>
+      <c r="M52" s="3">
         <v>1000</v>
-      </c>
-      <c r="M52" s="3">
-        <v>900</v>
       </c>
       <c r="N52" s="3">
         <v>900</v>
       </c>
       <c r="O52" s="3">
+        <v>900</v>
+      </c>
+      <c r="P52" s="3">
         <v>1000</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3228,8 +3348,11 @@
       <c r="V52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,50 +3413,53 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>388800</v>
+      </c>
+      <c r="E54" s="3">
         <v>355800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>361700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>378400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>464200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>475500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>509600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>670300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>699100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>727600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>687800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>635200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>636100</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>8</v>
       </c>
@@ -3352,8 +3478,11 @@
       <c r="V54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,50 +3530,51 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>32800</v>
+      </c>
+      <c r="E57" s="3">
         <v>23500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>28300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>27500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>20700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>16500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>20900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>33700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>28500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>17300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>25100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>22500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>19300</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>8</v>
       </c>
@@ -3462,28 +3593,31 @@
       <c r="V57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E58" s="3">
         <v>4700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6300</v>
-      </c>
-      <c r="I58" s="3">
-        <v>5600</v>
       </c>
       <c r="J58" s="3">
         <v>5600</v>
@@ -3498,14 +3632,14 @@
         <v>5600</v>
       </c>
       <c r="N58" s="3">
+        <v>5600</v>
+      </c>
+      <c r="O58" s="3">
         <v>5000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2900</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>8</v>
       </c>
@@ -3524,50 +3658,53 @@
       <c r="V58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>60800</v>
+      </c>
+      <c r="E59" s="3">
         <v>54300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>54400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>53000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>54000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>52900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>61800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>69500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>74900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>67100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>77300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>60000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>48900</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>8</v>
       </c>
@@ -3586,50 +3723,53 @@
       <c r="V59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>99800</v>
+      </c>
+      <c r="E60" s="3">
         <v>82500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>86000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>88100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>81700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>75800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>88300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>108800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>108900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>90000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>108000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>87500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>71100</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>8</v>
       </c>
@@ -3648,50 +3788,53 @@
       <c r="V60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>100600</v>
+      </c>
+      <c r="E61" s="3">
         <v>98800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>90100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>99000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>113000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>126100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>138000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>124300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>125600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>126900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>103200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>93200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>154200</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3710,50 +3853,53 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>51800</v>
+      </c>
+      <c r="E62" s="3">
         <v>38900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>37000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>37100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>39400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>38100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>36200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>37400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>38000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>42400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>25600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>45600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>52500</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>8</v>
       </c>
@@ -3772,8 +3918,11 @@
       <c r="V62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,50 +4113,53 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>252200</v>
+      </c>
+      <c r="E66" s="3">
         <v>220200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>213100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>224200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>234100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>240000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>262600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>270600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>272500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>259300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>236800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>226300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>426600</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>8</v>
       </c>
@@ -4020,8 +4178,11 @@
       <c r="V66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4230,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,50 +4463,53 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-278600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-276300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-267400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-253500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-183100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-178100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-168500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>18000</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>8</v>
       </c>
@@ -4354,8 +4528,11 @@
       <c r="V72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,50 +4723,53 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>136600</v>
+      </c>
+      <c r="E76" s="3">
         <v>135500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>148600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>154200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>230100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>235500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>247100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>399700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>426500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>468300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>451000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>408900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>209500</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>8</v>
       </c>
@@ -4602,8 +4788,11 @@
       <c r="V76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-13900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-70400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-173900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1500</v>
       </c>
-      <c r="M81" s="3">
-        <v>0</v>
-      </c>
       <c r="N81" s="3">
+        <v>0</v>
+      </c>
+      <c r="O81" s="3">
         <v>-9900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>7100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,8 +5015,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4826,47 +5025,47 @@
         <v>4300</v>
       </c>
       <c r="E83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F83" s="3">
         <v>4400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4200</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R83" s="3">
         <v>6800</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>8</v>
       </c>
@@ -4879,8 +5078,11 @@
       <c r="V83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,56 +5403,59 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>15400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>10800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>10300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>11100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>12200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-8700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-14900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>13200</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R89" s="3">
         <v>21700</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>8</v>
       </c>
@@ -5251,8 +5468,11 @@
       <c r="V89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,56 +5495,57 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-500</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-1800</v>
       </c>
       <c r="G91" s="3">
         <v>-1800</v>
       </c>
       <c r="H91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2000</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R91" s="3">
         <v>-1300</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>8</v>
       </c>
@@ -5337,8 +5558,11 @@
       <c r="V91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,56 +5688,59 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-500</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-1800</v>
       </c>
       <c r="G94" s="3">
         <v>-1800</v>
       </c>
       <c r="H94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="I94" s="3">
         <v>-1900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-26300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-22700</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R94" s="3">
         <v>-2400</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>8</v>
       </c>
@@ -5523,8 +5753,11 @@
       <c r="V94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5609,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,56 +6038,59 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E100" s="3">
         <v>8900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-14600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-14100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-12700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-11400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>13800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>22300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>8300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>30000</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R100" s="3">
         <v>1200</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>8</v>
       </c>
@@ -5857,56 +6103,59 @@
       <c r="V100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1200</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-100</v>
       </c>
       <c r="G101" s="3">
         <v>-100</v>
       </c>
       <c r="H101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-400</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R101" s="3">
         <v>700</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>8</v>
       </c>
@@ -5919,56 +6168,59 @@
       <c r="V101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-16100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>15300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-12900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-15600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>20100</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R102" s="3">
         <v>21300</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>8</v>
       </c>
@@ -5979,6 +6231,9 @@
         <v>8</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AKA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AKA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="92">
   <si>
     <t>AKA</t>
   </si>
@@ -656,171 +656,178 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>149900</v>
+      </c>
+      <c r="E8" s="3">
         <v>148900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>116800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>148900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>140800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>136000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>120500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>149100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>155800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>158500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>148300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>182400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>161800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>149200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>68800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>70800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>63300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>46800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>35000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>33800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>30300</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -828,129 +835,135 @@
         <v>63000</v>
       </c>
       <c r="E9" s="3">
+        <v>63000</v>
+      </c>
+      <c r="F9" s="3">
         <v>51200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>72500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>62900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>58700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>52000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>70400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>69000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>71000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>64100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>82900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>75700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>67800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>28200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>28100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>24800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>20800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>15800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>14700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>14200</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>85900</v>
+        <v>86900</v>
       </c>
       <c r="E10" s="3">
-        <v>65600</v>
+        <v>86000</v>
       </c>
       <c r="F10" s="3">
-        <v>76400</v>
+        <v>65700</v>
       </c>
       <c r="G10" s="3">
-        <v>77900</v>
+        <v>76500</v>
       </c>
       <c r="H10" s="3">
-        <v>77300</v>
+        <v>78000</v>
       </c>
       <c r="I10" s="3">
+        <v>77400</v>
+      </c>
+      <c r="J10" s="3">
         <v>68500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>78700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>86800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>87500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>84200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>99500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>86100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>81400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>40600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>42700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>38500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>26000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>19200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>19100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>16100</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -974,8 +987,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1039,8 +1053,11 @@
       <c r="W12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,8 +1121,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1115,39 +1135,39 @@
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>68500</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>173800</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>10900</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1160,8 +1180,8 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1169,50 +1189,53 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2700</v>
+        <v>4500</v>
       </c>
       <c r="E15" s="3">
-        <v>2800</v>
+        <v>4300</v>
       </c>
       <c r="F15" s="3">
-        <v>2700</v>
+        <v>4300</v>
       </c>
       <c r="G15" s="3">
+        <v>4400</v>
+      </c>
+      <c r="H15" s="3">
+        <v>4500</v>
+      </c>
+      <c r="I15" s="3">
+        <v>4700</v>
+      </c>
+      <c r="J15" s="3">
+        <v>5400</v>
+      </c>
+      <c r="K15" s="3">
         <v>2900</v>
       </c>
-      <c r="H15" s="3">
-        <v>2900</v>
-      </c>
-      <c r="I15" s="3">
-        <v>3000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>2900</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3700</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1225,8 +1248,8 @@
       <c r="T15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
+      <c r="U15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V15" s="3">
         <v>0</v>
@@ -1234,8 +1257,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>152000</v>
+      </c>
+      <c r="E17" s="3">
         <v>148300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>122900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>154300</v>
       </c>
-      <c r="G17" s="3">
-        <v>211200</v>
-      </c>
       <c r="H17" s="3">
+        <v>142700</v>
+      </c>
+      <c r="I17" s="3">
         <v>137100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>127000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>324700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>153100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>161000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>145000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>177200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>171500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>141900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>66100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>62900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>52400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>43300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>35000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>34200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>29100</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E18" s="3">
         <v>600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-6100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5400</v>
       </c>
-      <c r="G18" s="3">
-        <v>-70400</v>
-      </c>
       <c r="H18" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="I18" s="3">
         <v>-1100</v>
       </c>
-      <c r="I18" s="3">
-        <v>-6500</v>
-      </c>
       <c r="J18" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="K18" s="3">
         <v>-175600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-9700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>10900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3500</v>
       </c>
-      <c r="U18" s="3">
-        <v>0</v>
-      </c>
       <c r="V18" s="3">
+        <v>0</v>
+      </c>
+      <c r="W18" s="3">
         <v>-400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,138 +1444,145 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="E20" s="3">
-        <v>-500</v>
+        <v>-200</v>
       </c>
       <c r="F20" s="3">
-        <v>-100</v>
+        <v>500</v>
       </c>
       <c r="G20" s="3">
-        <v>-500</v>
+        <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>-700</v>
+        <v>500</v>
       </c>
       <c r="I20" s="3">
-        <v>-1000</v>
+        <v>800</v>
       </c>
       <c r="J20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-600</v>
       </c>
       <c r="O20" s="3">
         <v>-600</v>
       </c>
       <c r="P20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-4100</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-100</v>
       </c>
       <c r="R20" s="3">
         <v>-100</v>
       </c>
       <c r="S20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T20" s="3">
         <v>-200</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-100</v>
       </c>
       <c r="U20" s="3">
         <v>-100</v>
       </c>
       <c r="V20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E21" s="3">
         <v>5200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1000</v>
       </c>
-      <c r="G21" s="3">
-        <v>-66400</v>
-      </c>
       <c r="H21" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I21" s="3">
         <v>2900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-170100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>10000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-6100</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="3">
         <v>14500</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U21" s="3">
         <v>6400</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1550,41 +1590,41 @@
         <v>2700</v>
       </c>
       <c r="E22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F22" s="3">
         <v>2300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2700</v>
-      </c>
-      <c r="G22" s="3">
-        <v>2800</v>
       </c>
       <c r="H22" s="3">
         <v>2800</v>
       </c>
       <c r="I22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="J22" s="3">
         <v>2900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>4100</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>8</v>
       </c>
@@ -1597,8 +1637,8 @@
       <c r="T22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -1606,138 +1646,147 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-73700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-10400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-177600</v>
       </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
       <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
         <v>-5200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-14400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>10700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E24" s="3">
         <v>500</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>5800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-3300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-3700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-4300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1100</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>-100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-8900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-13900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-70400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-173900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1500</v>
       </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
       <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
         <v>-10100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>7300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-13900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-70400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-173900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1500</v>
       </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
       <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
         <v>-9900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>7100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2061,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,138 +2258,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-300</v>
+        <v>-800</v>
       </c>
       <c r="E32" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F32" s="3">
-        <v>100</v>
+        <v>-500</v>
       </c>
       <c r="G32" s="3">
-        <v>500</v>
+        <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>700</v>
+        <v>-500</v>
       </c>
       <c r="I32" s="3">
-        <v>1000</v>
+        <v>-800</v>
       </c>
       <c r="J32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
-      </c>
-      <c r="N32" s="3">
-        <v>600</v>
       </c>
       <c r="O32" s="3">
         <v>600</v>
       </c>
       <c r="P32" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q32" s="3">
         <v>4100</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>100</v>
       </c>
       <c r="R32" s="3">
         <v>100</v>
       </c>
       <c r="S32" s="3">
+        <v>100</v>
+      </c>
+      <c r="T32" s="3">
         <v>200</v>
-      </c>
-      <c r="T32" s="3">
-        <v>100</v>
       </c>
       <c r="U32" s="3">
         <v>100</v>
       </c>
       <c r="V32" s="3">
+        <v>100</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-13900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-70400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-173900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1500</v>
       </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
       <c r="O33" s="3">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3">
         <v>-9900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>7100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-13900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-70400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-173900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1500</v>
       </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
       <c r="O35" s="3">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3">
         <v>-9900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>7100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,53 +2657,54 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E41" s="3">
         <v>25500</v>
-      </c>
-      <c r="E41" s="3">
-        <v>21900</v>
       </c>
       <c r="F41" s="3">
         <v>21900</v>
       </c>
       <c r="G41" s="3">
+        <v>21900</v>
+      </c>
+      <c r="H41" s="3">
         <v>20700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>25900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>30200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>46300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>31100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>29100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>41200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>38800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>54400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>34300</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2636,8 +2723,11 @@
       <c r="W41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2701,53 +2791,56 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E43" s="3">
         <v>5800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6900</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>8</v>
       </c>
@@ -2766,53 +2859,56 @@
       <c r="W43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>106700</v>
+        <v>114300</v>
       </c>
       <c r="E44" s="3">
-        <v>91500</v>
+        <v>113100</v>
       </c>
       <c r="F44" s="3">
-        <v>91000</v>
+        <v>98500</v>
       </c>
       <c r="G44" s="3">
-        <v>100000</v>
+        <v>96000</v>
       </c>
       <c r="H44" s="3">
-        <v>106700</v>
+        <v>108000</v>
       </c>
       <c r="I44" s="3">
-        <v>112500</v>
+        <v>114100</v>
       </c>
       <c r="J44" s="3">
+        <v>116200</v>
+      </c>
+      <c r="K44" s="3">
         <v>126500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>136900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>143900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>120600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>115800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>95800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>99700</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>8</v>
       </c>
@@ -2831,53 +2927,56 @@
       <c r="W44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>17100</v>
+        <v>12200</v>
       </c>
       <c r="E45" s="3">
-        <v>16100</v>
+        <v>10700</v>
       </c>
       <c r="F45" s="3">
-        <v>18000</v>
+        <v>8800</v>
       </c>
       <c r="G45" s="3">
-        <v>30200</v>
+        <v>10900</v>
       </c>
       <c r="H45" s="3">
-        <v>25800</v>
+        <v>20200</v>
       </c>
       <c r="I45" s="3">
-        <v>22700</v>
+        <v>16400</v>
       </c>
       <c r="J45" s="3">
+        <v>17000</v>
+      </c>
+      <c r="K45" s="3">
         <v>21500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>28500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>32800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>31700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>27100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>22400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>15500</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>8</v>
       </c>
@@ -2896,53 +2995,56 @@
       <c r="W45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>156300</v>
+      </c>
+      <c r="E46" s="3">
         <v>155100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>133600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>135700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>154200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>161000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>168700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>197600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>200400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>208800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>197000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>184300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>176600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>156400</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>8</v>
       </c>
@@ -2961,31 +3063,34 @@
       <c r="W46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3026,53 +3131,56 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>91700</v>
+      </c>
+      <c r="E48" s="3">
         <v>77800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>65200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>64600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>65000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>67600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>66800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>66300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>64000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>57400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>59800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>41100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>39100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>38900</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>8</v>
       </c>
@@ -3091,8 +3199,11 @@
       <c r="W48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3100,44 +3211,44 @@
         <v>152100</v>
       </c>
       <c r="E49" s="3">
+        <v>152100</v>
+      </c>
+      <c r="F49" s="3">
         <v>153100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>159200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>157600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>233800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>238200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>243800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>404900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>431900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>469800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>461600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>418700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>439800</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>8</v>
       </c>
@@ -3156,8 +3267,11 @@
       <c r="W49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,53 +3403,56 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3800</v>
+        <v>2400</v>
       </c>
       <c r="E52" s="3">
-        <v>3800</v>
+        <v>2300</v>
       </c>
       <c r="F52" s="3">
         <v>2200</v>
       </c>
       <c r="G52" s="3">
-        <v>1700</v>
+        <v>600</v>
       </c>
       <c r="H52" s="3">
-        <v>1700</v>
+        <v>700</v>
       </c>
       <c r="I52" s="3">
-        <v>1700</v>
+        <v>700</v>
       </c>
       <c r="J52" s="3">
+        <v>800</v>
+      </c>
+      <c r="K52" s="3">
         <v>1900</v>
-      </c>
-      <c r="K52" s="3">
-        <v>900</v>
       </c>
       <c r="L52" s="3">
         <v>900</v>
       </c>
       <c r="M52" s="3">
+        <v>900</v>
+      </c>
+      <c r="N52" s="3">
         <v>1000</v>
-      </c>
-      <c r="N52" s="3">
-        <v>900</v>
       </c>
       <c r="O52" s="3">
         <v>900</v>
       </c>
       <c r="P52" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q52" s="3">
         <v>1000</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3351,8 +3471,11 @@
       <c r="W52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,53 +3539,56 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>404100</v>
+      </c>
+      <c r="E54" s="3">
         <v>388800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>355800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>361700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>378400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>464200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>475500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>509600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>670300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>699100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>727600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>687800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>635200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>636100</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>8</v>
       </c>
@@ -3481,8 +3607,11 @@
       <c r="W54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,53 +3661,54 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E57" s="3">
         <v>32800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>23500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>28300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>27500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>20700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>16500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>20900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>33700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>28500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>17300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>25100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>22500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>19300</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>8</v>
       </c>
@@ -3596,31 +3727,34 @@
       <c r="W57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>6300</v>
+        <v>13800</v>
       </c>
       <c r="E58" s="3">
-        <v>4700</v>
+        <v>13600</v>
       </c>
       <c r="F58" s="3">
-        <v>3300</v>
+        <v>12700</v>
       </c>
       <c r="G58" s="3">
-        <v>7700</v>
+        <v>10800</v>
       </c>
       <c r="H58" s="3">
-        <v>7000</v>
+        <v>14700</v>
       </c>
       <c r="I58" s="3">
-        <v>6300</v>
+        <v>13900</v>
       </c>
       <c r="J58" s="3">
-        <v>5600</v>
+        <v>12800</v>
       </c>
       <c r="K58" s="3">
         <v>5600</v>
@@ -3635,14 +3769,14 @@
         <v>5600</v>
       </c>
       <c r="O58" s="3">
+        <v>5600</v>
+      </c>
+      <c r="P58" s="3">
         <v>5000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2900</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
@@ -3661,53 +3795,56 @@
       <c r="W58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>60800</v>
+        <v>21200</v>
       </c>
       <c r="E59" s="3">
-        <v>54300</v>
+        <v>23800</v>
       </c>
       <c r="F59" s="3">
-        <v>54400</v>
+        <v>22600</v>
       </c>
       <c r="G59" s="3">
-        <v>53000</v>
+        <v>21600</v>
       </c>
       <c r="H59" s="3">
-        <v>54000</v>
+        <v>18400</v>
       </c>
       <c r="I59" s="3">
-        <v>52900</v>
+        <v>17300</v>
       </c>
       <c r="J59" s="3">
+        <v>15800</v>
+      </c>
+      <c r="K59" s="3">
         <v>61800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>69500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>74900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>67100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>77300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>60000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>48900</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>8</v>
       </c>
@@ -3726,53 +3863,56 @@
       <c r="W59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>98800</v>
+      </c>
+      <c r="E60" s="3">
         <v>99800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>82500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>86000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>88100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>81700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>75800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>88300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>108800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>108900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>90000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>108000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>87500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>71100</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>8</v>
       </c>
@@ -3791,53 +3931,56 @@
       <c r="W60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>100600</v>
+        <v>166500</v>
       </c>
       <c r="E61" s="3">
-        <v>98800</v>
+        <v>150800</v>
       </c>
       <c r="F61" s="3">
-        <v>90100</v>
+        <v>136200</v>
       </c>
       <c r="G61" s="3">
-        <v>99000</v>
+        <v>125400</v>
       </c>
       <c r="H61" s="3">
-        <v>113000</v>
+        <v>134300</v>
       </c>
       <c r="I61" s="3">
-        <v>126100</v>
+        <v>150600</v>
       </c>
       <c r="J61" s="3">
+        <v>162600</v>
+      </c>
+      <c r="K61" s="3">
         <v>138000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>124300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>125600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>126900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>103200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>93200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>154200</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3856,53 +3999,56 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>51800</v>
+        <v>1800</v>
       </c>
       <c r="E62" s="3">
-        <v>38900</v>
+        <v>1600</v>
       </c>
       <c r="F62" s="3">
-        <v>37000</v>
+        <v>1600</v>
       </c>
       <c r="G62" s="3">
-        <v>37100</v>
+        <v>1700</v>
       </c>
       <c r="H62" s="3">
-        <v>39400</v>
+        <v>1500</v>
       </c>
       <c r="I62" s="3">
-        <v>38100</v>
+        <v>1600</v>
       </c>
       <c r="J62" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K62" s="3">
         <v>36200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>37400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>38000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>42400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>25600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>45600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>52500</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>8</v>
       </c>
@@ -3921,8 +4067,11 @@
       <c r="W62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,53 +4271,56 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>267200</v>
+      </c>
+      <c r="E66" s="3">
         <v>252200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>220200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>213100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>224200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>234100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>240000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>262600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>270600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>272500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>259300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>236800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>226300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>426600</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>8</v>
       </c>
@@ -4181,8 +4339,11 @@
       <c r="W66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,53 +4637,56 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-284000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-278600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-276300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-267400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-253500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-183100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-178100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-168500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>18000</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>8</v>
       </c>
@@ -4531,8 +4705,11 @@
       <c r="W72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,53 +4909,56 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>136900</v>
+      </c>
+      <c r="E76" s="3">
         <v>136600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>135500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>148600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>154200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>230100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>235500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>247100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>399700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>426500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>468300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>451000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>408900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>209500</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>8</v>
       </c>
@@ -4791,8 +4977,11 @@
       <c r="W76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-13900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-70400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-173900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1500</v>
       </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
       <c r="O81" s="3">
+        <v>0</v>
+      </c>
+      <c r="P81" s="3">
         <v>-9900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>7100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,59 +5214,60 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>4300</v>
+        <v>1700</v>
       </c>
       <c r="E83" s="3">
-        <v>4300</v>
+        <v>1800</v>
       </c>
       <c r="F83" s="3">
-        <v>4400</v>
+        <v>2500</v>
       </c>
       <c r="G83" s="3">
-        <v>4500</v>
+        <v>2000</v>
       </c>
       <c r="H83" s="3">
-        <v>4700</v>
+        <v>1400</v>
       </c>
       <c r="I83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K83" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L83" s="3">
+        <v>4600</v>
+      </c>
+      <c r="M83" s="3">
+        <v>5600</v>
+      </c>
+      <c r="N83" s="3">
+        <v>5200</v>
+      </c>
+      <c r="O83" s="3">
         <v>5400</v>
       </c>
-      <c r="J83" s="3">
-        <v>5000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>4600</v>
-      </c>
-      <c r="L83" s="3">
-        <v>5600</v>
-      </c>
-      <c r="M83" s="3">
-        <v>5200</v>
-      </c>
-      <c r="N83" s="3">
-        <v>5400</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4200</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R83" s="3">
+      <c r="R83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S83" s="3">
         <v>6800</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>8</v>
       </c>
@@ -5081,8 +5280,11 @@
       <c r="W83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,59 +5620,62 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E89" s="3">
         <v>3500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>15400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>10800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>10300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>11100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>12200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-14900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>13200</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S89" s="3">
         <v>21700</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>8</v>
       </c>
@@ -5471,8 +5688,11 @@
       <c r="W89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,59 +5716,60 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-500</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-1800</v>
       </c>
       <c r="H91" s="3">
         <v>-1800</v>
       </c>
       <c r="I91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="J91" s="3">
         <v>-1900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2000</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R91" s="3">
+      <c r="R91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S91" s="3">
         <v>-1300</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>8</v>
       </c>
@@ -5561,8 +5782,11 @@
       <c r="W91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,59 +5918,62 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-500</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-1800</v>
       </c>
       <c r="H94" s="3">
         <v>-1800</v>
       </c>
       <c r="I94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="J94" s="3">
         <v>-1900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-26300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-22700</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R94" s="3">
+      <c r="R94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S94" s="3">
         <v>-2400</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>8</v>
       </c>
@@ -5756,8 +5986,11 @@
       <c r="W94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,31 +6014,32 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5846,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,59 +6284,62 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E100" s="3">
         <v>3100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>8900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-14600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-14100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-12700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-11400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>13800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>22300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>8300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>30000</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S100" s="3">
         <v>1200</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>8</v>
       </c>
@@ -6106,59 +6352,62 @@
       <c r="W100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-700</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
-        <v>-600</v>
+        <v>-100</v>
       </c>
       <c r="F101" s="3">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="G101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I101" s="3">
+        <v>500</v>
+      </c>
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="K101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M101" s="3">
+        <v>500</v>
+      </c>
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
-        <v>200</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-500</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="L101" s="3">
-        <v>500</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-400</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R101" s="3">
+      <c r="R101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S101" s="3">
         <v>700</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>8</v>
       </c>
@@ -6171,59 +6420,62 @@
       <c r="W101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E102" s="3">
         <v>3900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-16100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>15300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-12900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-15600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>20100</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R102" s="3">
+      <c r="R102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S102" s="3">
         <v>21300</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>8</v>
       </c>
@@ -6234,6 +6486,9 @@
         <v>8</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AKA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AKA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="92">
   <si>
     <t>AKA</t>
   </si>
@@ -656,314 +656,326 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>159000</v>
+      </c>
+      <c r="E8" s="3">
         <v>149900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>148900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>116800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>148900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>140800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>136000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>120500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>149100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>155800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>158500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>148300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>182400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>161800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>149200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>68800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>70800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>63300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>46800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>35000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>33800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>30300</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>63000</v>
+        <v>70100</v>
       </c>
       <c r="E9" s="3">
         <v>63000</v>
       </c>
       <c r="F9" s="3">
+        <v>63000</v>
+      </c>
+      <c r="G9" s="3">
         <v>51200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>72500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>62900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>58700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>52000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>70400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>69000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>71000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>64100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>82900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>75700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>67800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>28200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>28100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>24800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>20800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>15800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>14700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>14200</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>88900</v>
+      </c>
+      <c r="E10" s="3">
         <v>86900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>86000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>65700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>76500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>78000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>77400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>68500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>78700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>86800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>87500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>84200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>99500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>86100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>81400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>40600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>42700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>38500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>26000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>19200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>19100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>16100</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -988,8 +1000,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1056,8 +1069,11 @@
       <c r="X12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,13 +1140,16 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>2500</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1138,39 +1157,39 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H14" s="3">
+        <v>400</v>
+      </c>
+      <c r="I14" s="3">
         <v>68500</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>173800</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>10900</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1183,8 +1202,8 @@
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1192,53 +1211,56 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E15" s="3">
         <v>4500</v>
-      </c>
-      <c r="E15" s="3">
-        <v>4300</v>
       </c>
       <c r="F15" s="3">
         <v>4300</v>
       </c>
       <c r="G15" s="3">
+        <v>4300</v>
+      </c>
+      <c r="H15" s="3">
         <v>4400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3700</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1251,8 +1273,8 @@
       <c r="U15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V15" s="3">
-        <v>0</v>
+      <c r="V15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
@@ -1260,8 +1282,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1308,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>159300</v>
+      </c>
+      <c r="E17" s="3">
         <v>152000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>148300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>122900</v>
       </c>
-      <c r="G17" s="3">
-        <v>154300</v>
-      </c>
       <c r="H17" s="3">
+        <v>153900</v>
+      </c>
+      <c r="I17" s="3">
         <v>142700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>137100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>127000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>324700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>153100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>161000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>145000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>177200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>171500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>141900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>66100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>62900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>52400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>43300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>35000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>34200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>29100</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-6100</v>
       </c>
-      <c r="G18" s="3">
-        <v>-5400</v>
-      </c>
       <c r="H18" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-1800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-6600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-175600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-9700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>7300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>7900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>10900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3500</v>
       </c>
-      <c r="V18" s="3">
-        <v>0</v>
-      </c>
       <c r="W18" s="3">
+        <v>0</v>
+      </c>
+      <c r="X18" s="3">
         <v>-400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,189 +1477,196 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-600</v>
       </c>
       <c r="P20" s="3">
         <v>-600</v>
       </c>
       <c r="Q20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="R20" s="3">
         <v>-4100</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-100</v>
       </c>
       <c r="S20" s="3">
         <v>-100</v>
       </c>
       <c r="T20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U20" s="3">
         <v>-200</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-100</v>
       </c>
       <c r="V20" s="3">
         <v>-100</v>
       </c>
       <c r="W20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E21" s="3">
         <v>1600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2300</v>
       </c>
-      <c r="G21" s="3">
-        <v>-1000</v>
-      </c>
       <c r="H21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I21" s="3">
         <v>2200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-170100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>10000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T21" s="3">
         <v>14500</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V21" s="3">
         <v>6400</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2700</v>
+        <v>2600</v>
       </c>
       <c r="E22" s="3">
         <v>2700</v>
       </c>
       <c r="F22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="G22" s="3">
         <v>2300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2700</v>
-      </c>
-      <c r="H22" s="3">
-        <v>2800</v>
       </c>
       <c r="I22" s="3">
         <v>2800</v>
       </c>
       <c r="J22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K22" s="3">
         <v>2900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>4100</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>8</v>
       </c>
@@ -1640,8 +1679,8 @@
       <c r="U22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="V22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -1649,144 +1688,153 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-73700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-10400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-177600</v>
       </c>
-      <c r="L23" s="3">
-        <v>0</v>
-      </c>
       <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
         <v>-5200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-14400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>10700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>500</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>5800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-3300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-3700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1100</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>-100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1901,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-13900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-70400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-9600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-173900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1500</v>
       </c>
-      <c r="O26" s="3">
-        <v>0</v>
-      </c>
       <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-10100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>7300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-13900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-70400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-9600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-173900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1500</v>
       </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
       <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>7100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2114,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2185,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2256,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,144 +2327,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>600</v>
       </c>
       <c r="P32" s="3">
         <v>600</v>
       </c>
       <c r="Q32" s="3">
+        <v>600</v>
+      </c>
+      <c r="R32" s="3">
         <v>4100</v>
-      </c>
-      <c r="R32" s="3">
-        <v>100</v>
       </c>
       <c r="S32" s="3">
         <v>100</v>
       </c>
       <c r="T32" s="3">
+        <v>100</v>
+      </c>
+      <c r="U32" s="3">
         <v>200</v>
-      </c>
-      <c r="U32" s="3">
-        <v>100</v>
       </c>
       <c r="V32" s="3">
         <v>100</v>
       </c>
       <c r="W32" s="3">
+        <v>100</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-13900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-70400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-173900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1500</v>
       </c>
-      <c r="O33" s="3">
-        <v>0</v>
-      </c>
       <c r="P33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>7100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2540,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-13900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-70400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-173900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1500</v>
       </c>
-      <c r="O35" s="3">
-        <v>0</v>
-      </c>
       <c r="P35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>7100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2716,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,56 +2743,57 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E41" s="3">
         <v>23100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>25500</v>
-      </c>
-      <c r="F41" s="3">
-        <v>21900</v>
       </c>
       <c r="G41" s="3">
         <v>21900</v>
       </c>
       <c r="H41" s="3">
+        <v>21900</v>
+      </c>
+      <c r="I41" s="3">
         <v>20700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>25900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>30200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>46300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>31100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>29100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>41200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>38800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>54400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>34300</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2726,8 +2812,11 @@
       <c r="X41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2794,56 +2883,59 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E43" s="3">
         <v>6700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6900</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>8</v>
       </c>
@@ -2862,56 +2954,59 @@
       <c r="X43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>102400</v>
+      </c>
+      <c r="E44" s="3">
         <v>114300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>113100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>98500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>96000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>108000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>114100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>116200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>126500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>136900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>143900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>120600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>115800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>95800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>99700</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>8</v>
       </c>
@@ -2930,56 +3025,59 @@
       <c r="X44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E45" s="3">
         <v>12200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>10700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8800</v>
       </c>
-      <c r="G45" s="3">
-        <v>10900</v>
-      </c>
       <c r="H45" s="3">
+        <v>13000</v>
+      </c>
+      <c r="I45" s="3">
         <v>20200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>16400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>17000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>21500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>28500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>32800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>31700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>27100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>22400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>15500</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>8</v>
       </c>
@@ -2998,56 +3096,59 @@
       <c r="X45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>144800</v>
+      </c>
+      <c r="E46" s="3">
         <v>156300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>155100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>133600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>135700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>154200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>161000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>168700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>197600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>200400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>208800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>197000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>184300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>176600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>156400</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>8</v>
       </c>
@@ -3066,8 +3167,11 @@
       <c r="X46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3092,8 +3196,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3134,56 +3238,59 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>96600</v>
+      </c>
+      <c r="E48" s="3">
         <v>91700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>77800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>65200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>64600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>65000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>67600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>66800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>66300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>64000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>57400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>59800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>41100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>39100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>38900</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>8</v>
       </c>
@@ -3202,56 +3309,59 @@
       <c r="X48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>152100</v>
+        <v>141600</v>
       </c>
       <c r="E49" s="3">
         <v>152100</v>
       </c>
       <c r="F49" s="3">
+        <v>152100</v>
+      </c>
+      <c r="G49" s="3">
         <v>153100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>159200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>157600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>233800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>238200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>243800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>404900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>431900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>469800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>461600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>418700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>439800</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>8</v>
       </c>
@@ -3270,8 +3380,11 @@
       <c r="X49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3451,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,56 +3522,59 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E52" s="3">
         <v>2400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>600</v>
-      </c>
-      <c r="H52" s="3">
-        <v>700</v>
       </c>
       <c r="I52" s="3">
         <v>700</v>
       </c>
       <c r="J52" s="3">
+        <v>700</v>
+      </c>
+      <c r="K52" s="3">
         <v>800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1900</v>
-      </c>
-      <c r="L52" s="3">
-        <v>900</v>
       </c>
       <c r="M52" s="3">
         <v>900</v>
       </c>
       <c r="N52" s="3">
+        <v>900</v>
+      </c>
+      <c r="O52" s="3">
         <v>1000</v>
-      </c>
-      <c r="O52" s="3">
-        <v>900</v>
       </c>
       <c r="P52" s="3">
         <v>900</v>
       </c>
       <c r="Q52" s="3">
+        <v>900</v>
+      </c>
+      <c r="R52" s="3">
         <v>1000</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3474,8 +3593,11 @@
       <c r="X52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,56 +3664,59 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>385200</v>
+      </c>
+      <c r="E54" s="3">
         <v>404100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>388800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>355800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>361700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>378400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>464200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>475500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>509600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>670300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>699100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>727600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>687800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>635200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>636100</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>8</v>
       </c>
@@ -3610,8 +3735,11 @@
       <c r="X54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3764,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,56 +3791,57 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E57" s="3">
         <v>30600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>32800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>23500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>28300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>27500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>20700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>16500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>20900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>33700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>28500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>17300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>25100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>22500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>19300</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>8</v>
       </c>
@@ -3730,34 +3860,37 @@
       <c r="X57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E58" s="3">
         <v>13800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>13600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>14700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>13900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>12800</v>
-      </c>
-      <c r="K58" s="3">
-        <v>5600</v>
       </c>
       <c r="L58" s="3">
         <v>5600</v>
@@ -3772,14 +3905,14 @@
         <v>5600</v>
       </c>
       <c r="P58" s="3">
+        <v>5600</v>
+      </c>
+      <c r="Q58" s="3">
         <v>5000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2900</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>8</v>
       </c>
@@ -3798,56 +3931,59 @@
       <c r="X58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E59" s="3">
         <v>21200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>23800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>22600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>21600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>18400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>17300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>61800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>69500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>74900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>67100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>77300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>60000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>48900</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>8</v>
       </c>
@@ -3866,56 +4002,59 @@
       <c r="X59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E60" s="3">
         <v>98800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>99800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>82500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>86000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>88100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>81700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>75800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>88300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>108800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>108900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>90000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>108000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>87500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>71100</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>8</v>
       </c>
@@ -3934,56 +4073,59 @@
       <c r="X60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>168900</v>
+      </c>
+      <c r="E61" s="3">
         <v>166500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>150800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>136200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>125400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>134300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>150600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>162600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>138000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>124300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>125600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>126900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>103200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>93200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>154200</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4002,56 +4144,59 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E62" s="3">
         <v>1800</v>
-      </c>
-      <c r="E62" s="3">
-        <v>1600</v>
       </c>
       <c r="F62" s="3">
         <v>1600</v>
       </c>
       <c r="G62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H62" s="3">
         <v>1700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>36200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>37400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>38000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>42400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>25600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>45600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>52500</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>8</v>
       </c>
@@ -4070,8 +4215,11 @@
       <c r="X62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4286,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4357,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,56 +4428,59 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>267600</v>
+      </c>
+      <c r="E66" s="3">
         <v>267200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>252200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>220200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>213100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>224200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>234100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>240000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>262600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>270600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>272500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>259300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>236800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>226300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>426600</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>8</v>
       </c>
@@ -4342,8 +4499,11 @@
       <c r="X66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4528,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4597,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4668,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4572,8 +4739,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,56 +4810,59 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-293400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-284000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-278600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-276300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-267400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-253500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-183100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-178100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-168500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>18000</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>8</v>
       </c>
@@ -4708,8 +4881,11 @@
       <c r="X72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4952,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5023,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,56 +5094,59 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>117600</v>
+      </c>
+      <c r="E76" s="3">
         <v>136900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>136600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>135500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>148600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>154200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>230100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>235500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>247100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>399700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>426500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>468300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>451000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>408900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>209500</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>8</v>
       </c>
@@ -4980,8 +5165,11 @@
       <c r="X76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5236,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-13900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-70400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-173900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1500</v>
       </c>
-      <c r="O81" s="3">
-        <v>0</v>
-      </c>
       <c r="P81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>7100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,8 +5412,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5224,53 +5422,53 @@
         <v>1700</v>
       </c>
       <c r="E83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F83" s="3">
         <v>1800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4200</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T83" s="3">
         <v>6800</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>8</v>
       </c>
@@ -5283,8 +5481,11 @@
       <c r="X83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5552,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5623,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5694,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5765,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,62 +5836,65 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-7700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>15400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>10800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>10300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>11100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>12200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-8700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-14900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>13200</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T89" s="3">
         <v>21700</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>8</v>
       </c>
@@ -5691,8 +5907,11 @@
       <c r="X89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,62 +5936,63 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-500</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-1800</v>
       </c>
       <c r="I91" s="3">
         <v>-1800</v>
       </c>
       <c r="J91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S91" s="3">
+      <c r="S91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T91" s="3">
         <v>-1300</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>8</v>
       </c>
@@ -5785,8 +6005,11 @@
       <c r="X91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6076,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,62 +6147,65 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-500</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-1800</v>
       </c>
       <c r="I94" s="3">
         <v>-1800</v>
       </c>
       <c r="J94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-26300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-22700</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T94" s="3">
         <v>-2400</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>8</v>
       </c>
@@ -5989,8 +6218,11 @@
       <c r="X94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6247,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6041,8 +6274,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6083,8 +6316,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6387,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6458,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,62 +6529,65 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E100" s="3">
         <v>4200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>8900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-14600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-14100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-12700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-11400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>13800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>22300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>8300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>30000</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T100" s="3">
         <v>1200</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>8</v>
       </c>
@@ -6355,62 +6600,65 @@
       <c r="X100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-100</v>
+        <v>1200</v>
       </c>
       <c r="E101" s="3">
         <v>-100</v>
       </c>
       <c r="F101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-400</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T101" s="3">
         <v>700</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>8</v>
       </c>
@@ -6423,62 +6671,65 @@
       <c r="X101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-16100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>15300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-12900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-15600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>20100</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T102" s="3">
         <v>21300</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>8</v>
       </c>
@@ -6489,6 +6740,9 @@
         <v>8</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AKA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AKA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="92">
   <si>
     <t>AKA</t>
   </si>
@@ -656,326 +656,339 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>128700</v>
+      </c>
+      <c r="E8" s="3">
         <v>159000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>149900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>148900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>116800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>148900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>140800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>136000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>120500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>149100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>155800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>158500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>148300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>182400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>161800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>149200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>68800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>70800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>63300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>46800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>35000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>33800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>30300</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E9" s="3">
         <v>70100</v>
-      </c>
-      <c r="E9" s="3">
-        <v>63000</v>
       </c>
       <c r="F9" s="3">
         <v>63000</v>
       </c>
       <c r="G9" s="3">
+        <v>63000</v>
+      </c>
+      <c r="H9" s="3">
         <v>51200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>72500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>62900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>58700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>52000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>70400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>69000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>71000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>64100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>82900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>75700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>67800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>28200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>28100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>24800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>20800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>15800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>14700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>14200</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>73700</v>
+      </c>
+      <c r="E10" s="3">
         <v>88900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>86900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>86000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>65700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>76500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>78000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>77400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>68500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>78700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>86800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>87500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>84200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>99500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>86100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>81400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>40600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>42700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>38500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>26000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>19200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>19100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>16100</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1001,8 +1014,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1072,8 +1086,11 @@
       <c r="Y12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1143,56 +1160,59 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>2500</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>68500</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>173800</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>10900</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1205,8 +1225,8 @@
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1214,56 +1234,59 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E15" s="3">
         <v>4600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4500</v>
-      </c>
-      <c r="F15" s="3">
-        <v>4300</v>
       </c>
       <c r="G15" s="3">
         <v>4300</v>
       </c>
       <c r="H15" s="3">
+        <v>4300</v>
+      </c>
+      <c r="I15" s="3">
         <v>4400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3700</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1276,8 +1299,8 @@
       <c r="V15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W15" s="3">
-        <v>0</v>
+      <c r="W15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X15" s="3">
         <v>0</v>
@@ -1285,8 +1308,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1309,150 +1335,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>134000</v>
+      </c>
+      <c r="E17" s="3">
         <v>159300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>152000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>148300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>122900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>153900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>142700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>137100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>127000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>324700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>153100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>161000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>145000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>177200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>171500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>141900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>66100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>62900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>52400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>43300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>35000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>34200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>29100</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-6100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-175600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-9700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>10900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3500</v>
       </c>
-      <c r="W18" s="3">
-        <v>0</v>
-      </c>
       <c r="X18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1478,198 +1511,205 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-600</v>
       </c>
       <c r="Q20" s="3">
         <v>-600</v>
       </c>
       <c r="R20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="S20" s="3">
         <v>-4100</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-100</v>
       </c>
       <c r="T20" s="3">
         <v>-100</v>
       </c>
       <c r="U20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V20" s="3">
         <v>-200</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-100</v>
       </c>
       <c r="W20" s="3">
         <v>-100</v>
       </c>
       <c r="X20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E21" s="3">
         <v>4300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-170100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>10000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-6100</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U21" s="3">
         <v>14500</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W21" s="3">
         <v>6400</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E22" s="3">
         <v>2600</v>
-      </c>
-      <c r="E22" s="3">
-        <v>2700</v>
       </c>
       <c r="F22" s="3">
         <v>2700</v>
       </c>
       <c r="G22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="H22" s="3">
         <v>2300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2700</v>
-      </c>
-      <c r="I22" s="3">
-        <v>2800</v>
       </c>
       <c r="J22" s="3">
         <v>2800</v>
       </c>
       <c r="K22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="L22" s="3">
         <v>2900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>4100</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>8</v>
       </c>
@@ -1682,8 +1722,8 @@
       <c r="V22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="W22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -1691,150 +1731,159 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-8100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-73700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-10400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-177600</v>
       </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
       <c r="N23" s="3">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
         <v>-5200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-14400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>7700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>10700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>3900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>500</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>5800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-3300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-3700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-4300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1100</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>-100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1904,150 +1953,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-13900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-70400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-173900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1500</v>
       </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
       <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3">
         <v>-10100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>7300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-13900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-70400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-173900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1500</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
       <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3">
         <v>-9900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>7100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2117,8 +2175,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2188,8 +2249,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2259,8 +2323,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2330,150 +2397,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
-      </c>
-      <c r="P32" s="3">
-        <v>600</v>
       </c>
       <c r="Q32" s="3">
         <v>600</v>
       </c>
       <c r="R32" s="3">
+        <v>600</v>
+      </c>
+      <c r="S32" s="3">
         <v>4100</v>
-      </c>
-      <c r="S32" s="3">
-        <v>100</v>
       </c>
       <c r="T32" s="3">
         <v>100</v>
       </c>
       <c r="U32" s="3">
+        <v>100</v>
+      </c>
+      <c r="V32" s="3">
         <v>200</v>
-      </c>
-      <c r="V32" s="3">
-        <v>100</v>
       </c>
       <c r="W32" s="3">
         <v>100</v>
       </c>
       <c r="X32" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-13900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-70400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-173900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1500</v>
       </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
       <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3">
         <v>-9900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>7100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2543,155 +2619,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-13900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-70400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-173900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1500</v>
       </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
       <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3">
         <v>-9900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>7100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2717,8 +2802,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2744,59 +2830,60 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E41" s="3">
         <v>24200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>23100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>25500</v>
-      </c>
-      <c r="G41" s="3">
-        <v>21900</v>
       </c>
       <c r="H41" s="3">
         <v>21900</v>
       </c>
       <c r="I41" s="3">
+        <v>21900</v>
+      </c>
+      <c r="J41" s="3">
         <v>20700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>25900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>30200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>46300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>31100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>29100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>41200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>38800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>54400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>34300</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2815,8 +2902,11 @@
       <c r="Y41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2886,59 +2976,62 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E43" s="3">
         <v>8100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6900</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>8</v>
       </c>
@@ -2957,59 +3050,62 @@
       <c r="Y43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>99700</v>
+      </c>
+      <c r="E44" s="3">
         <v>102400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>114300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>113100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>98500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>96000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>108000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>114100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>116200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>126500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>136900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>143900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>120600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>115800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>95800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>99700</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>8</v>
       </c>
@@ -3028,59 +3124,62 @@
       <c r="Y44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E45" s="3">
         <v>10000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>10700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>8800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>13000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>20200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>16400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>17000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>21500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>28500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>32800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>31700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>27100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>22400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>15500</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3099,59 +3198,62 @@
       <c r="Y45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>148800</v>
+      </c>
+      <c r="E46" s="3">
         <v>144800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>156300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>155100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>133600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>135700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>154200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>161000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>168700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>197600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>200400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>208800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>197000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>184300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>176600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>156400</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>8</v>
       </c>
@@ -3170,8 +3272,11 @@
       <c r="Y46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3199,8 +3304,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3241,59 +3346,62 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>106100</v>
+      </c>
+      <c r="E48" s="3">
         <v>96600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>91700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>77800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>65200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>64600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>65000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>67600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>66800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>66300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>64000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>57400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>59800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>41100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>39100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>38900</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>8</v>
       </c>
@@ -3312,59 +3420,62 @@
       <c r="Y48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>139500</v>
+      </c>
+      <c r="E49" s="3">
         <v>141600</v>
-      </c>
-      <c r="E49" s="3">
-        <v>152100</v>
       </c>
       <c r="F49" s="3">
         <v>152100</v>
       </c>
       <c r="G49" s="3">
+        <v>152100</v>
+      </c>
+      <c r="H49" s="3">
         <v>153100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>159200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>157600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>233800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>238200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>243800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>404900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>431900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>469800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>461600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>418700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>439800</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>8</v>
       </c>
@@ -3383,8 +3494,11 @@
       <c r="Y49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3454,8 +3568,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3525,8 +3642,11 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3534,50 +3654,50 @@
         <v>2100</v>
       </c>
       <c r="E52" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F52" s="3">
         <v>2400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>600</v>
-      </c>
-      <c r="I52" s="3">
-        <v>700</v>
       </c>
       <c r="J52" s="3">
         <v>700</v>
       </c>
       <c r="K52" s="3">
+        <v>700</v>
+      </c>
+      <c r="L52" s="3">
         <v>800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1900</v>
-      </c>
-      <c r="M52" s="3">
-        <v>900</v>
       </c>
       <c r="N52" s="3">
         <v>900</v>
       </c>
       <c r="O52" s="3">
+        <v>900</v>
+      </c>
+      <c r="P52" s="3">
         <v>1000</v>
-      </c>
-      <c r="P52" s="3">
-        <v>900</v>
       </c>
       <c r="Q52" s="3">
         <v>900</v>
       </c>
       <c r="R52" s="3">
+        <v>900</v>
+      </c>
+      <c r="S52" s="3">
         <v>1000</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3596,8 +3716,11 @@
       <c r="Y52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3667,59 +3790,62 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>396600</v>
+      </c>
+      <c r="E54" s="3">
         <v>385200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>404100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>388800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>355800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>361700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>378400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>464200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>475500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>509600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>670300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>699100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>727600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>687800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>635200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>636100</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>8</v>
       </c>
@@ -3738,8 +3864,11 @@
       <c r="Y54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3765,8 +3894,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3792,59 +3922,60 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E57" s="3">
         <v>30300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>30600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>32800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>23500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>28300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>27500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>20700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>16500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>20900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>33700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>28500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>17300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>25100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>22500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>19300</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>8</v>
       </c>
@@ -3863,37 +3994,40 @@
       <c r="Y57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E58" s="3">
         <v>14700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>13800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>13600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>14700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>13900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12800</v>
-      </c>
-      <c r="L58" s="3">
-        <v>5600</v>
       </c>
       <c r="M58" s="3">
         <v>5600</v>
@@ -3908,14 +4042,14 @@
         <v>5600</v>
       </c>
       <c r="Q58" s="3">
+        <v>5600</v>
+      </c>
+      <c r="R58" s="3">
         <v>5000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2900</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
@@ -3934,59 +4068,62 @@
       <c r="Y58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E59" s="3">
         <v>20800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>21200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>23800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>22600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>21600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>18400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>17300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>61800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>69500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>74900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>67100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>77300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>60000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>48900</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4005,59 +4142,62 @@
       <c r="Y59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E60" s="3">
         <v>97000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>98800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>99800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>82500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>86000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>88100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>81700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>75800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>88300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>108800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>108900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>90000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>108000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>87500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>71100</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>8</v>
       </c>
@@ -4076,59 +4216,62 @@
       <c r="Y60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>185300</v>
+      </c>
+      <c r="E61" s="3">
         <v>168900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>166500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>150800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>136200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>125400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>134300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>150600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>162600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>138000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>124300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>125600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>126900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>103200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>93200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>154200</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4147,59 +4290,62 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E62" s="3">
         <v>1600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1800</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1600</v>
       </c>
       <c r="G62" s="3">
         <v>1600</v>
       </c>
       <c r="H62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I62" s="3">
         <v>1700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>36200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>37400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>38000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>42400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>25600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>45600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>52500</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>8</v>
       </c>
@@ -4218,8 +4364,11 @@
       <c r="Y62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4289,8 +4438,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4360,8 +4512,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4431,59 +4586,62 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>285100</v>
+      </c>
+      <c r="E66" s="3">
         <v>267600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>267200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>252200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>220200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>213100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>224200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>234100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>240000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>262600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>270600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>272500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>259300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>236800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>226300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>426600</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>8</v>
       </c>
@@ -4502,8 +4660,11 @@
       <c r="Y66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4529,8 +4690,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4600,8 +4762,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4671,8 +4836,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4742,8 +4910,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4813,59 +4984,62 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-301800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-293400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-284000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-278600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-276300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-267400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-253500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-183100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-178100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-168500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>18000</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>8</v>
       </c>
@@ -4884,8 +5058,11 @@
       <c r="Y72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4955,8 +5132,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5026,8 +5206,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5097,59 +5280,62 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>111500</v>
+      </c>
+      <c r="E76" s="3">
         <v>117600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>136900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>136600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>135500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>148600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>154200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>230100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>235500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>247100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>399700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>426500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>468300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>451000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>408900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>209500</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>8</v>
       </c>
@@ -5168,8 +5354,11 @@
       <c r="Y76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5239,155 +5428,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-13900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-70400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-173900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1500</v>
       </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
       <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+      <c r="R81" s="3">
         <v>-9900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>7100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5413,65 +5611,66 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1700</v>
+        <v>1500</v>
       </c>
       <c r="E83" s="3">
         <v>1700</v>
       </c>
       <c r="F83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G83" s="3">
         <v>1800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4200</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T83" s="3">
+      <c r="T83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U83" s="3">
         <v>6800</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>8</v>
       </c>
@@ -5484,8 +5683,11 @@
       <c r="Y83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5555,8 +5757,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5626,8 +5831,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5697,8 +5905,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5768,8 +5979,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5839,65 +6053,68 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E89" s="3">
         <v>7000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>15400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>10800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>10300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>11100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>12200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-8700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-14900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>13200</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T89" s="3">
+      <c r="T89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U89" s="3">
         <v>21700</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>8</v>
       </c>
@@ -5910,8 +6127,11 @@
       <c r="Y89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5937,65 +6157,66 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-500</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-1800</v>
       </c>
       <c r="J91" s="3">
         <v>-1800</v>
       </c>
       <c r="K91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="L91" s="3">
         <v>-1900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2000</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T91" s="3">
+      <c r="T91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U91" s="3">
         <v>-1300</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>8</v>
       </c>
@@ -6008,8 +6229,11 @@
       <c r="Y91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6079,8 +6303,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6150,65 +6377,68 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-500</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-1800</v>
       </c>
       <c r="J94" s="3">
         <v>-1800</v>
       </c>
       <c r="K94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="L94" s="3">
         <v>-1900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-26300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-22700</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T94" s="3">
+      <c r="T94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U94" s="3">
         <v>-2400</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>8</v>
       </c>
@@ -6221,8 +6451,11 @@
       <c r="Y94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6248,8 +6481,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6277,8 +6511,8 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6319,8 +6553,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6390,8 +6627,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6461,8 +6701,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6532,65 +6775,68 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>8900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-14600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-14100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-12700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-11400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>13800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>22300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>8300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>30000</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T100" s="3">
+      <c r="T100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U100" s="3">
         <v>1200</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>8</v>
       </c>
@@ -6603,65 +6849,68 @@
       <c r="Y100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E101" s="3">
         <v>1200</v>
-      </c>
-      <c r="E101" s="3">
-        <v>-100</v>
       </c>
       <c r="F101" s="3">
         <v>-100</v>
       </c>
       <c r="G101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-400</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T101" s="3">
+      <c r="T101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U101" s="3">
         <v>700</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>8</v>
       </c>
@@ -6674,65 +6923,68 @@
       <c r="Y101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E102" s="3">
         <v>900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-16100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>15300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-12900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>20100</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T102" s="3">
+      <c r="T102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U102" s="3">
         <v>21300</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>8</v>
       </c>
@@ -6743,6 +6995,9 @@
         <v>8</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AKA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AKA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="92">
   <si>
     <t>AKA</t>
   </si>
@@ -656,339 +656,352 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>160500</v>
+      </c>
+      <c r="E8" s="3">
         <v>128700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>159000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>149900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>148900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>116800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>148900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>140800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>136000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>120500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>149100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>155800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>158500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>148300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>182400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>161800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>149200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>68800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>70800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>63300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>46800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>35000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>33800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>30300</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>68200</v>
+      </c>
+      <c r="E9" s="3">
         <v>55000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>70100</v>
-      </c>
-      <c r="F9" s="3">
-        <v>63000</v>
       </c>
       <c r="G9" s="3">
         <v>63000</v>
       </c>
       <c r="H9" s="3">
+        <v>63000</v>
+      </c>
+      <c r="I9" s="3">
         <v>51200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>72500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>62900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>58700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>52000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>70400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>69000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>71000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>64100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>82900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>75700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>67800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>28200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>28100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>24800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>20800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>15800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>14700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>14200</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>92300</v>
+      </c>
+      <c r="E10" s="3">
         <v>73700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>88900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>86900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>86000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>65700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>76500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>78000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>77400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>68500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>78700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>86800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>87500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>84200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>99500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>86100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>81400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>40600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>42700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>38500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>26000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>19200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>19100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>16100</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1015,8 +1028,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1089,8 +1103,11 @@
       <c r="Z12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1163,59 +1180,62 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>2500</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>68500</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>173800</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>10900</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1228,8 +1248,8 @@
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1237,59 +1257,62 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E15" s="3">
         <v>4400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4500</v>
-      </c>
-      <c r="G15" s="3">
-        <v>4300</v>
       </c>
       <c r="H15" s="3">
         <v>4300</v>
       </c>
       <c r="I15" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J15" s="3">
         <v>4400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3700</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1302,8 +1325,8 @@
       <c r="W15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X15" s="3">
-        <v>0</v>
+      <c r="X15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y15" s="3">
         <v>0</v>
@@ -1311,8 +1334,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>161000</v>
+      </c>
+      <c r="E17" s="3">
         <v>134000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>159300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>152000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>148300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>122900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>153900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>142700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>137100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>127000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>324700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>153100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>161000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>145000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>177200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>171500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>141900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>66100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>62900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>52400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>43300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>35000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>34200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>29100</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-6100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-175600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-9700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>7300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>7900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>10900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3500</v>
       </c>
-      <c r="X18" s="3">
-        <v>0</v>
-      </c>
       <c r="Y18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,207 +1545,214 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>600</v>
+      </c>
+      <c r="E20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-600</v>
       </c>
       <c r="R20" s="3">
         <v>-600</v>
       </c>
       <c r="S20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="T20" s="3">
         <v>-4100</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-100</v>
       </c>
       <c r="U20" s="3">
         <v>-100</v>
       </c>
       <c r="V20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W20" s="3">
         <v>-200</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-100</v>
       </c>
       <c r="X20" s="3">
         <v>-100</v>
       </c>
       <c r="Y20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-170100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>10000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-6100</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V21" s="3">
         <v>14500</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X21" s="3">
         <v>6400</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E22" s="3">
         <v>2700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2600</v>
-      </c>
-      <c r="F22" s="3">
-        <v>2700</v>
       </c>
       <c r="G22" s="3">
         <v>2700</v>
       </c>
       <c r="H22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I22" s="3">
         <v>2300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2700</v>
-      </c>
-      <c r="J22" s="3">
-        <v>2800</v>
       </c>
       <c r="K22" s="3">
         <v>2800</v>
       </c>
       <c r="L22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="M22" s="3">
         <v>2900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>4100</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>8</v>
       </c>
@@ -1725,8 +1765,8 @@
       <c r="W22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
+      <c r="X22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
@@ -1734,82 +1774,88 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-8900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-73700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-10400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-177600</v>
       </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
       <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
         <v>-5200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-14400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>7700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>10700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1817,73 +1863,76 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>3900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>500</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>5800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-3300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-3700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-4300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1100</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-8900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-13900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-70400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-173900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1500</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
       <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
         <v>-10100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>5300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>7300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-8900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-13900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-70400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-173900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1500</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
       <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
         <v>-9900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>5100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>7100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2252,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,156 +2467,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>600</v>
       </c>
       <c r="R32" s="3">
         <v>600</v>
       </c>
       <c r="S32" s="3">
+        <v>600</v>
+      </c>
+      <c r="T32" s="3">
         <v>4100</v>
-      </c>
-      <c r="T32" s="3">
-        <v>100</v>
       </c>
       <c r="U32" s="3">
         <v>100</v>
       </c>
       <c r="V32" s="3">
+        <v>100</v>
+      </c>
+      <c r="W32" s="3">
         <v>200</v>
-      </c>
-      <c r="W32" s="3">
-        <v>100</v>
       </c>
       <c r="X32" s="3">
         <v>100</v>
       </c>
       <c r="Y32" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-8900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-13900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-70400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-173900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1500</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
       <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
         <v>-9900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>7100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-8900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-13900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-70400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-173900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1500</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
       <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
         <v>-9900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>7100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,62 +2917,63 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E41" s="3">
         <v>26700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>24200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>23100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>25500</v>
-      </c>
-      <c r="H41" s="3">
-        <v>21900</v>
       </c>
       <c r="I41" s="3">
         <v>21900</v>
       </c>
       <c r="J41" s="3">
+        <v>21900</v>
+      </c>
+      <c r="K41" s="3">
         <v>20700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>25900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>30200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>46300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>31100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>29100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>41200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>38800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>54400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>34300</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2905,8 +2992,11 @@
       <c r="Z41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2979,62 +3069,65 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E43" s="3">
         <v>13400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6900</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3053,62 +3146,65 @@
       <c r="Z43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>94700</v>
+      </c>
+      <c r="E44" s="3">
         <v>99700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>102400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>114300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>113100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>98500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>96000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>108000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>114100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>116200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>126500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>136900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>143900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>120600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>115800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>95800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>99700</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>8</v>
       </c>
@@ -3127,62 +3223,65 @@
       <c r="Z44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E45" s="3">
         <v>9000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>10000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>20200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>16400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>17000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>21500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>28500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>32800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>31700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>27100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>22400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>15500</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3201,62 +3300,65 @@
       <c r="Z45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>155200</v>
+      </c>
+      <c r="E46" s="3">
         <v>148800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>144800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>156300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>155100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>133600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>135700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>154200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>161000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>168700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>197600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>200400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>208800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>197000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>184300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>176600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>156400</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>8</v>
       </c>
@@ -3275,8 +3377,11 @@
       <c r="Z46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3307,8 +3412,8 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3349,62 +3454,65 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>113200</v>
+      </c>
+      <c r="E48" s="3">
         <v>106100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>96600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>91700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>77800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>65200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>64600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>65000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>67600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>66800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>66300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>64000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>57400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>59800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>41100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>39100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>38900</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>8</v>
       </c>
@@ -3423,62 +3531,65 @@
       <c r="Z48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>140200</v>
+      </c>
+      <c r="E49" s="3">
         <v>139500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>141600</v>
-      </c>
-      <c r="F49" s="3">
-        <v>152100</v>
       </c>
       <c r="G49" s="3">
         <v>152100</v>
       </c>
       <c r="H49" s="3">
+        <v>152100</v>
+      </c>
+      <c r="I49" s="3">
         <v>153100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>159200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>157600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>233800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>238200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>243800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>404900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>431900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>469800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>461600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>418700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>439800</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>8</v>
       </c>
@@ -3497,8 +3608,11 @@
       <c r="Z49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,62 +3762,65 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="E52" s="3">
         <v>2100</v>
       </c>
       <c r="F52" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G52" s="3">
         <v>2400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>600</v>
-      </c>
-      <c r="J52" s="3">
-        <v>700</v>
       </c>
       <c r="K52" s="3">
         <v>700</v>
       </c>
       <c r="L52" s="3">
+        <v>700</v>
+      </c>
+      <c r="M52" s="3">
         <v>800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1900</v>
-      </c>
-      <c r="N52" s="3">
-        <v>900</v>
       </c>
       <c r="O52" s="3">
         <v>900</v>
       </c>
       <c r="P52" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q52" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>900</v>
       </c>
       <c r="R52" s="3">
         <v>900</v>
       </c>
       <c r="S52" s="3">
+        <v>900</v>
+      </c>
+      <c r="T52" s="3">
         <v>1000</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3719,8 +3839,11 @@
       <c r="Z52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,62 +3916,65 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>410800</v>
+      </c>
+      <c r="E54" s="3">
         <v>396600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>385200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>404100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>388800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>355800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>361700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>378400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>464200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>475500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>509600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>670300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>699100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>727600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>687800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>635200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>636100</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>8</v>
       </c>
@@ -3867,8 +3993,11 @@
       <c r="Z54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,62 +4053,63 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>43600</v>
+      </c>
+      <c r="E57" s="3">
         <v>27400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>30300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>30600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>32800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>23500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>28300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>27500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>20700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>16500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>20900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>33700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>28500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>17300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>25100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>22500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>19300</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>8</v>
       </c>
@@ -3997,40 +4128,43 @@
       <c r="Z57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E58" s="3">
         <v>15900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>14700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>13800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>13600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>12700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>14700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>13900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>12800</v>
-      </c>
-      <c r="M58" s="3">
-        <v>5600</v>
       </c>
       <c r="N58" s="3">
         <v>5600</v>
@@ -4045,14 +4179,14 @@
         <v>5600</v>
       </c>
       <c r="R58" s="3">
+        <v>5600</v>
+      </c>
+      <c r="S58" s="3">
         <v>5000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2900</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>8</v>
       </c>
@@ -4071,62 +4205,65 @@
       <c r="Z58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E59" s="3">
         <v>23500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>20800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>21200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>23800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>22600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>21600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>18400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>61800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>69500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>74900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>67100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>77300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>60000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>48900</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4145,62 +4282,65 @@
       <c r="Z59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>117200</v>
+      </c>
+      <c r="E60" s="3">
         <v>98000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>97000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>98800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>99800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>82500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>86000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>88100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>81700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>75800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>88300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>108800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>108900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>90000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>108000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>87500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>71100</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>8</v>
       </c>
@@ -4219,62 +4359,65 @@
       <c r="Z60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>177500</v>
+      </c>
+      <c r="E61" s="3">
         <v>185300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>168900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>166500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>150800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>136200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>125400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>134300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>150600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>162600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>138000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>124300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>125600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>126900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>103200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>93200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>154200</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4293,62 +4436,65 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1800</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1600</v>
       </c>
       <c r="H62" s="3">
         <v>1600</v>
       </c>
       <c r="I62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J62" s="3">
         <v>1700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>36200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>37400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>38000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>42400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>25600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>45600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>52500</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>8</v>
       </c>
@@ -4367,8 +4513,11 @@
       <c r="Z62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,62 +4744,65 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>296700</v>
+      </c>
+      <c r="E66" s="3">
         <v>285100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>267600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>267200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>252200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>220200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>213100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>224200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>234100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>240000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>262600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>270600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>272500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>259300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>236800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>226300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>426600</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>8</v>
       </c>
@@ -4663,8 +4821,11 @@
       <c r="Z66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4913,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,62 +5158,65 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-305400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-301800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-293400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-284000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-278600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-276300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-267400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-253500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-183100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-178100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-168500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>18000</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>8</v>
       </c>
@@ -5061,8 +5235,11 @@
       <c r="Z72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,62 +5466,65 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>114100</v>
+      </c>
+      <c r="E76" s="3">
         <v>111500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>117600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>136900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>136600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>135500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>148600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>154200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>230100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>235500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>247100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>399700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>426500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>468300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>451000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>408900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>209500</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>8</v>
       </c>
@@ -5357,8 +5543,11 @@
       <c r="Z76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-8900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-13900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-70400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-173900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1500</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
       <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
         <v>-9900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>7100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,8 +5810,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5621,59 +5820,59 @@
         <v>1500</v>
       </c>
       <c r="E83" s="3">
-        <v>1700</v>
+        <v>1500</v>
       </c>
       <c r="F83" s="3">
         <v>1700</v>
       </c>
       <c r="G83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H83" s="3">
         <v>1800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4200</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V83" s="3">
         <v>6800</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>8</v>
       </c>
@@ -5686,8 +5885,11 @@
       <c r="Z83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,68 +6270,71 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>15400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>10800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>10300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>11100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>12200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-8700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-14900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>13200</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V89" s="3">
         <v>21700</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>8</v>
       </c>
@@ -6130,8 +6347,11 @@
       <c r="Z89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,68 +6378,69 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-500</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-1800</v>
       </c>
       <c r="K91" s="3">
         <v>-1800</v>
       </c>
       <c r="L91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="M91" s="3">
         <v>-1900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2000</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U91" s="3">
+      <c r="U91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V91" s="3">
         <v>-1300</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>8</v>
       </c>
@@ -6232,8 +6453,11 @@
       <c r="Z91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,68 +6607,71 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-500</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-1800</v>
       </c>
       <c r="K94" s="3">
         <v>-1800</v>
       </c>
       <c r="L94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="M94" s="3">
         <v>-1900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-26300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-22700</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V94" s="3">
         <v>-2400</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>8</v>
       </c>
@@ -6454,8 +6684,11 @@
       <c r="Z94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6514,8 +6748,8 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6556,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,68 +7021,71 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E100" s="3">
         <v>7600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>8900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-14600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-14100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-12700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-11400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>13800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>22300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>8300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>30000</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V100" s="3">
         <v>1200</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>8</v>
       </c>
@@ -6852,68 +7098,71 @@
       <c r="Z100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1200</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-100</v>
       </c>
       <c r="G101" s="3">
         <v>-100</v>
       </c>
       <c r="H101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-400</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U101" s="3">
+      <c r="U101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V101" s="3">
         <v>700</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W101" s="3" t="s">
         <v>8</v>
       </c>
@@ -6926,68 +7175,71 @@
       <c r="Z101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E102" s="3">
         <v>2400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-16100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>15300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-12900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-15600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>20100</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V102" s="3">
         <v>21300</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>8</v>
       </c>
@@ -6998,6 +7250,9 @@
         <v>8</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AKA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AKA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="92">
   <si>
     <t>AKA</t>
   </si>
@@ -656,365 +656,377 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>164000</v>
+      </c>
+      <c r="E8" s="3">
         <v>147100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>160500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>128700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>159000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>149900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>148900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>116800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>148900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>140800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>136000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>120500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>149100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>155800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>158500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>148300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>182400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>161800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>149200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>68800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>70800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>63300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>46800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>35000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>33800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>30300</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>72900</v>
+      </c>
+      <c r="E9" s="3">
         <v>60100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>68200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>55000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>70100</v>
-      </c>
-      <c r="H9" s="3">
-        <v>63000</v>
       </c>
       <c r="I9" s="3">
         <v>63000</v>
       </c>
       <c r="J9" s="3">
+        <v>63000</v>
+      </c>
+      <c r="K9" s="3">
         <v>51200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>72500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>62900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>58700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>52000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>70400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>69000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>71000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>64100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>82900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>75700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>67800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>28200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>28100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>24800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>20800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>15800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>14700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>14200</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>91100</v>
+      </c>
+      <c r="E10" s="3">
         <v>87000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>92300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>73700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>88900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>86900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>86000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>65700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>76500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>78000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>77400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>68500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>78700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>86800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>87500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>84200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>99500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>86100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>81400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>40600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>42700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>38500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>26000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>19200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>19100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>16100</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,8 +1055,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1123,8 +1136,11 @@
       <c r="AB12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,65 +1219,68 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E14" s="3">
         <v>200</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I14" s="3">
         <v>2500</v>
       </c>
-      <c r="H14" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>68500</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>173800</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>10900</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1274,8 +1293,8 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1283,65 +1302,68 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E15" s="3">
         <v>4600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4500</v>
-      </c>
-      <c r="I15" s="3">
-        <v>4300</v>
       </c>
       <c r="J15" s="3">
         <v>4300</v>
       </c>
       <c r="K15" s="3">
+        <v>4300</v>
+      </c>
+      <c r="L15" s="3">
         <v>4400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>5400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>3700</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1354,8 +1376,8 @@
       <c r="Y15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z15" s="3">
-        <v>0</v>
+      <c r="Z15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA15" s="3">
         <v>0</v>
@@ -1363,8 +1385,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1415,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>170500</v>
+      </c>
+      <c r="E17" s="3">
         <v>148300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>161000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>134000</v>
       </c>
-      <c r="G17" s="3">
-        <v>159300</v>
-      </c>
       <c r="H17" s="3">
+        <v>158900</v>
+      </c>
+      <c r="I17" s="3">
         <v>149500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>148300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>122900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>153900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>142700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>137100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>127000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>324700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>153100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>161000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>145000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>177200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>171500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>141900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>66100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>62900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>52400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>43300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>35000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>34200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>29100</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5400</v>
       </c>
-      <c r="G18" s="3">
-        <v>-300</v>
-      </c>
       <c r="H18" s="3">
+        <v>200</v>
+      </c>
+      <c r="I18" s="3">
         <v>400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-6100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-175600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>5200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-9700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>7300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>7900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>10900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3500</v>
       </c>
-      <c r="Z18" s="3">
-        <v>0</v>
-      </c>
       <c r="AA18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,225 +1612,232 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-600</v>
       </c>
       <c r="T20" s="3">
         <v>-600</v>
       </c>
       <c r="U20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="V20" s="3">
         <v>-4100</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-100</v>
       </c>
       <c r="W20" s="3">
         <v>-100</v>
       </c>
       <c r="X20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-200</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-100</v>
       </c>
       <c r="Z20" s="3">
         <v>-100</v>
       </c>
       <c r="AA20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E21" s="3">
         <v>3100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1300</v>
       </c>
-      <c r="G21" s="3">
-        <v>4300</v>
-      </c>
       <c r="H21" s="3">
+        <v>4700</v>
+      </c>
+      <c r="I21" s="3">
         <v>4100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-170100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>8700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>10000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-6100</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X21" s="3">
         <v>14500</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z21" s="3">
         <v>6400</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E22" s="3">
         <v>2400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2600</v>
-      </c>
-      <c r="H22" s="3">
-        <v>2700</v>
       </c>
       <c r="I22" s="3">
         <v>2700</v>
       </c>
       <c r="J22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="K22" s="3">
         <v>2300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2700</v>
-      </c>
-      <c r="L22" s="3">
-        <v>2800</v>
       </c>
       <c r="M22" s="3">
         <v>2800</v>
       </c>
       <c r="N22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="O22" s="3">
         <v>2900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>4100</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>8</v>
       </c>
@@ -1811,8 +1850,8 @@
       <c r="Y22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
+      <c r="Z22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
@@ -1820,168 +1859,177 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-73700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-10400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-177600</v>
       </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
       <c r="Q23" s="3">
+        <v>0</v>
+      </c>
+      <c r="R23" s="3">
         <v>-5200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-14400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>7700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>10700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E24" s="3">
         <v>900</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>3900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>500</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>5800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-3300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-3700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-4300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1100</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>-100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2108,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-8900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-13900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-70400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-173900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1500</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
       <c r="T26" s="3">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3">
         <v>-10100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>5300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>7300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-13900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-70400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-173900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1500</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
       <c r="T27" s="3">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3">
         <v>-9900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>7100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2357,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2380,8 +2440,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2523,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,168 +2606,177 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
-      </c>
-      <c r="S32" s="3">
-        <v>600</v>
       </c>
       <c r="T32" s="3">
         <v>600</v>
       </c>
       <c r="U32" s="3">
+        <v>600</v>
+      </c>
+      <c r="V32" s="3">
         <v>4100</v>
-      </c>
-      <c r="V32" s="3">
-        <v>100</v>
       </c>
       <c r="W32" s="3">
         <v>100</v>
       </c>
       <c r="X32" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y32" s="3">
         <v>200</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>100</v>
       </c>
       <c r="Z32" s="3">
         <v>100</v>
       </c>
       <c r="AA32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-13900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-70400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-173900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1500</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3">
         <v>-9900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>7100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2855,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-13900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-70400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-173900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1500</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3">
         <v>-9900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>7100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3059,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,68 +3090,69 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E41" s="3">
         <v>23400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>23100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>26700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>24200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>23100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>25500</v>
-      </c>
-      <c r="J41" s="3">
-        <v>21900</v>
       </c>
       <c r="K41" s="3">
         <v>21900</v>
       </c>
       <c r="L41" s="3">
+        <v>21900</v>
+      </c>
+      <c r="M41" s="3">
         <v>20700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>25900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>30200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>46300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>31100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>29100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>41200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>38800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>54400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>34300</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3085,8 +3171,11 @@
       <c r="AB41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3165,68 +3254,71 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E43" s="3">
         <v>8200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>24900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>13400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6900</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3245,68 +3337,71 @@
       <c r="AB43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>88800</v>
+      </c>
+      <c r="E44" s="3">
         <v>101600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>94700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>99700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>102400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>114300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>113100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>98500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>96000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>108000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>114100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>116200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>126500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>136900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>143900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>120600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>115800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>95800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>99700</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W44" s="3" t="s">
         <v>8</v>
       </c>
@@ -3325,68 +3420,71 @@
       <c r="AB44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E45" s="3">
         <v>11000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>12200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>10700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>20200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>16400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>17000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>21500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>28500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>32800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>31700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>27100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>22400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>15500</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3405,68 +3503,71 @@
       <c r="AB45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>129500</v>
+      </c>
+      <c r="E46" s="3">
         <v>145000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>155200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>148800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>144800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>156300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>155100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>133600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>135700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>154200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>161000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>168700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>197600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>200400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>208800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>197000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>184300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>176600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>156400</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>8</v>
       </c>
@@ -3485,8 +3586,11 @@
       <c r="AB46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3523,8 +3627,8 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3565,68 +3669,71 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>127900</v>
+      </c>
+      <c r="E48" s="3">
         <v>125100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>113200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>106100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>96600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>91700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>77800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>65200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>64600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>65000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>67600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>66800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>66300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>64000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>57400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>59800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>41100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>39100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>38900</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>8</v>
       </c>
@@ -3645,68 +3752,71 @@
       <c r="AB48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>137200</v>
+      </c>
+      <c r="E49" s="3">
         <v>138800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>140200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>139500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>141600</v>
-      </c>
-      <c r="H49" s="3">
-        <v>152100</v>
       </c>
       <c r="I49" s="3">
         <v>152100</v>
       </c>
       <c r="J49" s="3">
+        <v>152100</v>
+      </c>
+      <c r="K49" s="3">
         <v>153100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>159200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>157600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>233800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>238200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>243800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>404900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>431900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>469800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>461600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>418700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>439800</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>8</v>
       </c>
@@ -3725,8 +3835,11 @@
       <c r="AB49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3918,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,68 +4001,71 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E52" s="3">
         <v>2500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2200</v>
-      </c>
-      <c r="F52" s="3">
-        <v>2100</v>
       </c>
       <c r="G52" s="3">
         <v>2100</v>
       </c>
       <c r="H52" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I52" s="3">
         <v>2400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>600</v>
-      </c>
-      <c r="L52" s="3">
-        <v>700</v>
       </c>
       <c r="M52" s="3">
         <v>700</v>
       </c>
       <c r="N52" s="3">
+        <v>700</v>
+      </c>
+      <c r="O52" s="3">
         <v>800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1900</v>
-      </c>
-      <c r="P52" s="3">
-        <v>900</v>
       </c>
       <c r="Q52" s="3">
         <v>900</v>
       </c>
       <c r="R52" s="3">
+        <v>900</v>
+      </c>
+      <c r="S52" s="3">
         <v>1000</v>
-      </c>
-      <c r="S52" s="3">
-        <v>900</v>
       </c>
       <c r="T52" s="3">
         <v>900</v>
       </c>
       <c r="U52" s="3">
+        <v>900</v>
+      </c>
+      <c r="V52" s="3">
         <v>1000</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3965,8 +4084,11 @@
       <c r="AB52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,68 +4167,71 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>397400</v>
+      </c>
+      <c r="E54" s="3">
         <v>411300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>410800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>396600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>385200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>404100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>388800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>355800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>361700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>378400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>464200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>475500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>509600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>670300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>699100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>727600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>687800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>635200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>636100</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4125,8 +4250,11 @@
       <c r="AB54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4283,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,68 +4314,69 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E57" s="3">
         <v>38000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>43600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>27400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>30300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>30600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>32800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>23500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>28300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>27500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>20700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>16500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>20900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>33700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>28500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>17300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>25100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>22500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>19300</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>8</v>
       </c>
@@ -4265,46 +4395,49 @@
       <c r="AB57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E58" s="3">
         <v>19100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>17800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>15900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>14700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>13800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>13600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>12700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>14700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>13900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>12800</v>
-      </c>
-      <c r="O58" s="3">
-        <v>5600</v>
       </c>
       <c r="P58" s="3">
         <v>5600</v>
@@ -4319,14 +4452,14 @@
         <v>5600</v>
       </c>
       <c r="T58" s="3">
+        <v>5600</v>
+      </c>
+      <c r="U58" s="3">
         <v>5000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2900</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>8</v>
       </c>
@@ -4345,68 +4478,71 @@
       <c r="AB58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E59" s="3">
         <v>19900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>22600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>23500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>20800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>21200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>23800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>22600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>21600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>18400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>61800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>69500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>74900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>67100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>77300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>60000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>48900</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4425,68 +4561,71 @@
       <c r="AB59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>105000</v>
+      </c>
+      <c r="E60" s="3">
         <v>107600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>117200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>98000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>97000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>98800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>99800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>82500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>86000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>88100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>81700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>75800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>88300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>108800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>108900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>90000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>108000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>87500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>71100</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>8</v>
       </c>
@@ -4505,68 +4644,71 @@
       <c r="AB60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>192400</v>
+      </c>
+      <c r="E61" s="3">
         <v>191700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>177500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>185300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>168900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>166500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>150800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>136200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>125400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>134300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>150600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>162600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>138000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>124300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>125600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>126900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>103200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>93200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>154200</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4585,68 +4727,71 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E62" s="3">
         <v>1900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1800</v>
-      </c>
-      <c r="I62" s="3">
-        <v>1600</v>
       </c>
       <c r="J62" s="3">
         <v>1600</v>
       </c>
       <c r="K62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L62" s="3">
         <v>1700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>36200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>37400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>38000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>42400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>25600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>45600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>52500</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>8</v>
       </c>
@@ -4665,8 +4810,11 @@
       <c r="AB62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4893,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4976,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,68 +5059,71 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>299600</v>
+      </c>
+      <c r="E66" s="3">
         <v>301200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>296700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>285100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>267600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>267200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>252200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>220200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>213100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>224200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>234100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>240000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>262600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>270600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>272500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>259300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>236800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>226300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>426600</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>8</v>
       </c>
@@ -4985,8 +5142,11 @@
       <c r="AB66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5175,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5256,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5339,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5422,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,68 +5505,71 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-324800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-310300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-305400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-301800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-293400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-284000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-278600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-276300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-267400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-253500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-183100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-178100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-168500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>9700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>18000</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>8</v>
       </c>
@@ -5415,8 +5588,11 @@
       <c r="AB72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5671,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5754,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,68 +5837,71 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>97800</v>
+      </c>
+      <c r="E76" s="3">
         <v>110100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>114100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>111500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>117600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>136900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>136600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>135500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>148600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>154200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>230100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>235500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>247100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>399700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>426500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>468300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>451000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>408900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>209500</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>8</v>
       </c>
@@ -5735,8 +5920,11 @@
       <c r="AB76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6003,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-13900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-70400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-173900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1500</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3">
         <v>-9900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>7100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,74 +6207,75 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E83" s="3">
         <v>1700</v>
-      </c>
-      <c r="E83" s="3">
-        <v>1500</v>
       </c>
       <c r="F83" s="3">
         <v>1500</v>
       </c>
       <c r="G83" s="3">
-        <v>1700</v>
+        <v>1500</v>
       </c>
       <c r="H83" s="3">
         <v>1700</v>
       </c>
       <c r="I83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J83" s="3">
         <v>1800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4200</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X83" s="3">
         <v>6800</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>8</v>
       </c>
@@ -6090,8 +6288,11 @@
       <c r="AB83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6371,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6454,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6537,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6620,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,74 +6703,77 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E89" s="3">
         <v>4700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>11900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-7700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>15400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>10800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>10300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>11100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>12200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-8700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-14900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>13200</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X89" s="3">
         <v>21700</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>8</v>
       </c>
@@ -6570,8 +6786,11 @@
       <c r="AB89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,74 +6819,75 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-500</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-1800</v>
       </c>
       <c r="M91" s="3">
         <v>-1800</v>
       </c>
       <c r="N91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="O91" s="3">
         <v>-1900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2000</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X91" s="3">
         <v>-1300</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>8</v>
       </c>
@@ -6680,8 +6900,11 @@
       <c r="AB91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6983,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,74 +7066,77 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-500</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-1800</v>
       </c>
       <c r="M94" s="3">
         <v>-1800</v>
       </c>
       <c r="N94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="O94" s="3">
         <v>-1900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-26300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-22700</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X94" s="3">
         <v>-2400</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>8</v>
       </c>
@@ -6920,8 +7149,11 @@
       <c r="AB94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7182,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6988,8 +7221,8 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7030,8 +7263,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7346,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7429,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,74 +7512,77 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E100" s="3">
         <v>500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-11400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>7600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>4200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>8900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-14600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-14100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-12700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-11400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>13800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>22300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>8300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>30000</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X100" s="3">
         <v>1200</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>8</v>
       </c>
@@ -7350,74 +7595,77 @@
       <c r="AB100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E101" s="3">
         <v>600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1200</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-100</v>
       </c>
       <c r="I101" s="3">
         <v>-100</v>
       </c>
       <c r="J101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-400</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W101" s="3">
+      <c r="W101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X101" s="3">
         <v>700</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y101" s="3" t="s">
         <v>8</v>
       </c>
@@ -7430,74 +7678,77 @@
       <c r="AB101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E102" s="3">
         <v>800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-16100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>15300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-12900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-15600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>20100</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X102" s="3">
         <v>21300</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>8</v>
       </c>
@@ -7508,6 +7759,9 @@
         <v>8</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AKA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AKA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
   <si>
     <t>AKA</t>
   </si>
@@ -656,377 +656,390 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>132500</v>
+      </c>
+      <c r="E8" s="3">
         <v>164000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>147100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>160500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>128700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>159000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>149900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>148900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>116800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>148900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>140800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>136000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>120500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>149100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>155800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>158500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>148300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>182400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>161800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>149200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>68800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>70800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>63300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>46800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>35000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>33800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>30300</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>48800</v>
+      </c>
+      <c r="E9" s="3">
         <v>72900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>60100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>68200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>55000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>70100</v>
-      </c>
-      <c r="I9" s="3">
-        <v>63000</v>
       </c>
       <c r="J9" s="3">
         <v>63000</v>
       </c>
       <c r="K9" s="3">
+        <v>63000</v>
+      </c>
+      <c r="L9" s="3">
         <v>51200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>72500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>62900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>58700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>52000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>70400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>69000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>71000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>64100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>82900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>75700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>67800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>28200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>28100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>24800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>20800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>15800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>14700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>14200</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>83600</v>
+      </c>
+      <c r="E10" s="3">
         <v>91100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>87000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>92300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>73700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>88900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>86900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>86000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>65700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>76500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>78000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>77400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>68500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>78700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>86800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>87500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>84200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>99500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>86100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>81400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>40600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>42700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>38500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>26000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>19200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>19100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>16100</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1056,8 +1069,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,8 +1153,11 @@
       <c r="AC12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1222,68 +1239,71 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>4200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>200</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>3000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2500</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>68500</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>173800</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>10900</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1296,8 +1316,8 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1305,68 +1325,71 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E15" s="3">
         <v>4500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4500</v>
-      </c>
-      <c r="J15" s="3">
-        <v>4300</v>
       </c>
       <c r="K15" s="3">
         <v>4300</v>
       </c>
       <c r="L15" s="3">
+        <v>4300</v>
+      </c>
+      <c r="M15" s="3">
         <v>4400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>5400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>3700</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1379,8 +1402,8 @@
       <c r="Z15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA15" s="3">
-        <v>0</v>
+      <c r="AA15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB15" s="3">
         <v>0</v>
@@ -1388,8 +1411,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1416,174 +1442,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>136600</v>
+      </c>
+      <c r="E17" s="3">
         <v>170500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>148300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>161000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>134000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>158900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>149500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>148300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>122900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>153900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>142700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>137100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>127000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>324700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>153100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>161000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>145000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>177200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>171500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>141900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>66100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>62900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>52400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>43300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>35000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>34200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>29100</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-6500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-5400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-6600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-175600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-9700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>7300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>7900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>10900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3500</v>
       </c>
-      <c r="AA18" s="3">
-        <v>0</v>
-      </c>
       <c r="AB18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1613,234 +1646,241 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>600</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>100</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-600</v>
       </c>
       <c r="U20" s="3">
         <v>-600</v>
       </c>
       <c r="V20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="W20" s="3">
         <v>-4100</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-100</v>
       </c>
       <c r="X20" s="3">
         <v>-100</v>
       </c>
       <c r="Y20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-100</v>
       </c>
       <c r="AA20" s="3">
         <v>-100</v>
       </c>
       <c r="AB20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-170100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>10000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-6100</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y21" s="3">
         <v>14500</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA21" s="3">
         <v>6400</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E22" s="3">
         <v>2500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2600</v>
-      </c>
-      <c r="I22" s="3">
-        <v>2700</v>
       </c>
       <c r="J22" s="3">
         <v>2700</v>
       </c>
       <c r="K22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="L22" s="3">
         <v>2300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2700</v>
-      </c>
-      <c r="M22" s="3">
-        <v>2800</v>
       </c>
       <c r="N22" s="3">
         <v>2800</v>
       </c>
       <c r="O22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="P22" s="3">
         <v>2900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>4100</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W22" s="3" t="s">
         <v>8</v>
       </c>
@@ -1853,8 +1893,8 @@
       <c r="Z22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="AA22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -1862,174 +1902,183 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-13300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-73700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-10400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-177600</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
       <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
         <v>-5200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-14400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>7700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>10700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>900</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>3900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>500</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>5800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-3300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-4300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1100</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
       <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>-100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2111,174 +2160,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-14500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-8900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-13900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-70400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-173900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1500</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
       <c r="U26" s="3">
+        <v>0</v>
+      </c>
+      <c r="V26" s="3">
         <v>-10100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>7300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-14500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-8900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-13900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-70400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-173900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1500</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
       <c r="U27" s="3">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3">
         <v>-9900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>7100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2360,8 +2418,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2443,8 +2504,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2526,8 +2590,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2609,174 +2676,183 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-100</v>
-      </c>
-      <c r="T32" s="3">
-        <v>600</v>
       </c>
       <c r="U32" s="3">
         <v>600</v>
       </c>
       <c r="V32" s="3">
+        <v>600</v>
+      </c>
+      <c r="W32" s="3">
         <v>4100</v>
-      </c>
-      <c r="W32" s="3">
-        <v>100</v>
       </c>
       <c r="X32" s="3">
         <v>100</v>
       </c>
       <c r="Y32" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z32" s="3">
         <v>200</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>100</v>
       </c>
       <c r="AA32" s="3">
         <v>100</v>
       </c>
       <c r="AB32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-14500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-8900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-13900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-70400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-173900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1500</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
       <c r="U33" s="3">
+        <v>0</v>
+      </c>
+      <c r="V33" s="3">
         <v>-9900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>7100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2858,179 +2934,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-14500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-8900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-13900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-70400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-173900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1500</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
       <c r="U35" s="3">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3">
         <v>-9900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>7100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3060,8 +3145,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3091,71 +3177,72 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E41" s="3">
         <v>20300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>23400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>23100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>26700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>24200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>23100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>25500</v>
-      </c>
-      <c r="K41" s="3">
-        <v>21900</v>
       </c>
       <c r="L41" s="3">
         <v>21900</v>
       </c>
       <c r="M41" s="3">
+        <v>21900</v>
+      </c>
+      <c r="N41" s="3">
         <v>20700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>25900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>30200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>46300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>31100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>29100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>41200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>38800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>54400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>34300</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3174,8 +3261,11 @@
       <c r="AC41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3257,71 +3347,74 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E43" s="3">
         <v>10700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>24900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>13400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6900</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3340,71 +3433,74 @@
       <c r="AC43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>67700</v>
+      </c>
+      <c r="E44" s="3">
         <v>88800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>101600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>94700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>99700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>102400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>114300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>113100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>98500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>96000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>108000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>114100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>116200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>126500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>136900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>143900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>120600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>115800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>95800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>99700</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>8</v>
       </c>
@@ -3423,71 +3519,74 @@
       <c r="AC44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>9700</v>
       </c>
-      <c r="E45" s="3">
-        <v>11000</v>
-      </c>
       <c r="F45" s="3">
+        <v>11700</v>
+      </c>
+      <c r="G45" s="3">
         <v>12500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>9000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>10000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>12200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>20200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>16400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>17000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>21500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>28500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>32800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>31700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>27100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>22400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>15500</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3506,71 +3605,74 @@
       <c r="AC45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>125400</v>
+      </c>
+      <c r="E46" s="3">
         <v>129500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>145000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>155200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>148800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>144800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>156300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>155100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>133600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>135700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>154200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>161000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>168700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>197600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>200400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>208800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>197000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>184300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>176600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>156400</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>8</v>
       </c>
@@ -3589,8 +3691,11 @@
       <c r="AC46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3630,8 +3735,8 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3672,71 +3777,74 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>132800</v>
+      </c>
+      <c r="E48" s="3">
         <v>127900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>125100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>113200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>106100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>96600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>91700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>77800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>65200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>64600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>65000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>67600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>66800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>66300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>64000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>57400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>59800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>41100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>39100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>38900</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>8</v>
       </c>
@@ -3755,71 +3863,74 @@
       <c r="AC48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>136700</v>
+      </c>
+      <c r="E49" s="3">
         <v>137200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>138800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>140200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>139500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>141600</v>
-      </c>
-      <c r="I49" s="3">
-        <v>152100</v>
       </c>
       <c r="J49" s="3">
         <v>152100</v>
       </c>
       <c r="K49" s="3">
+        <v>152100</v>
+      </c>
+      <c r="L49" s="3">
         <v>153100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>159200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>157600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>233800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>238200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>243800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>404900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>431900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>469800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>461600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>418700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>439800</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>8</v>
       </c>
@@ -3838,8 +3949,11 @@
       <c r="AC49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3921,8 +4035,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4004,8 +4121,11 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4013,62 +4133,62 @@
         <v>2800</v>
       </c>
       <c r="E52" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F52" s="3">
         <v>2500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2200</v>
-      </c>
-      <c r="G52" s="3">
-        <v>2100</v>
       </c>
       <c r="H52" s="3">
         <v>2100</v>
       </c>
       <c r="I52" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J52" s="3">
         <v>2400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>600</v>
-      </c>
-      <c r="M52" s="3">
-        <v>700</v>
       </c>
       <c r="N52" s="3">
         <v>700</v>
       </c>
       <c r="O52" s="3">
+        <v>700</v>
+      </c>
+      <c r="P52" s="3">
         <v>800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1900</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>900</v>
       </c>
       <c r="R52" s="3">
         <v>900</v>
       </c>
       <c r="S52" s="3">
+        <v>900</v>
+      </c>
+      <c r="T52" s="3">
         <v>1000</v>
-      </c>
-      <c r="T52" s="3">
-        <v>900</v>
       </c>
       <c r="U52" s="3">
         <v>900</v>
       </c>
       <c r="V52" s="3">
+        <v>900</v>
+      </c>
+      <c r="W52" s="3">
         <v>1000</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4087,8 +4207,11 @@
       <c r="AC52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4170,71 +4293,74 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>397700</v>
+      </c>
+      <c r="E54" s="3">
         <v>397400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>411300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>410800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>396600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>385200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>404100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>388800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>355800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>361700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>378400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>464200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>475500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>509600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>670300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>699100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>727600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>687800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>635200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>636100</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4253,8 +4379,11 @@
       <c r="AC54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4284,8 +4413,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4315,71 +4445,72 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>29500</v>
+      </c>
+      <c r="E57" s="3">
         <v>31200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>38000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>43600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>27400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>30300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>30600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>32800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>23500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>28300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>27500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>20700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>16500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>20900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>33700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>28500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>17300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>25100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>22500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>19300</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>8</v>
       </c>
@@ -4398,49 +4529,52 @@
       <c r="AC57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E58" s="3">
         <v>19400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>19100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>17800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>15900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>14700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>13800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>13600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>10800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>14700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>13900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>12800</v>
-      </c>
-      <c r="P58" s="3">
-        <v>5600</v>
       </c>
       <c r="Q58" s="3">
         <v>5600</v>
@@ -4455,14 +4589,14 @@
         <v>5600</v>
       </c>
       <c r="U58" s="3">
+        <v>5600</v>
+      </c>
+      <c r="V58" s="3">
         <v>5000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2900</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>8</v>
       </c>
@@ -4481,71 +4615,74 @@
       <c r="AC58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E59" s="3">
         <v>20800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>19900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>22600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>23500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>20800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>21200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>23800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>22600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>21600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>18400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>61800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>69500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>74900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>67100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>77300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>60000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>48900</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4564,71 +4701,74 @@
       <c r="AC59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>105500</v>
+      </c>
+      <c r="E60" s="3">
         <v>105000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>107600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>117200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>98000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>97000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>98800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>99800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>82500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>86000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>88100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>81700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>75800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>88300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>108800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>108900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>90000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>108000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>87500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>71100</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>8</v>
       </c>
@@ -4647,71 +4787,74 @@
       <c r="AC60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>195800</v>
+      </c>
+      <c r="E61" s="3">
         <v>192400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>191700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>177500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>185300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>168900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>166500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>150800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>136200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>125400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>134300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>150600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>162600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>138000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>124300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>125600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>126900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>103200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>93200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>154200</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4730,71 +4873,74 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1800</v>
-      </c>
-      <c r="J62" s="3">
-        <v>1600</v>
       </c>
       <c r="K62" s="3">
         <v>1600</v>
       </c>
       <c r="L62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M62" s="3">
         <v>1700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>36200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>37400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>38000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>42400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>25600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>45600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>52500</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>8</v>
       </c>
@@ -4813,8 +4959,11 @@
       <c r="AC62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4896,8 +5045,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4979,8 +5131,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5062,71 +5217,74 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>303300</v>
+      </c>
+      <c r="E66" s="3">
         <v>299600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>301200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>296700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>285100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>267600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>267200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>252200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>220200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>213100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>224200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>234100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>240000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>262600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>270600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>272500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>259300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>236800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>226300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>426600</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>8</v>
       </c>
@@ -5145,8 +5303,11 @@
       <c r="AC66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5176,8 +5337,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5259,8 +5421,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5342,8 +5507,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5425,8 +5593,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5508,71 +5679,74 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-332000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-324800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-310300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-305400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-301800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-293400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-284000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-278600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-276300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-267400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-253500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-183100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-178100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-168500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>9700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>18000</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>8</v>
       </c>
@@ -5591,8 +5765,11 @@
       <c r="AC72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5674,8 +5851,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5757,8 +5937,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5840,71 +6023,74 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>94400</v>
+      </c>
+      <c r="E76" s="3">
         <v>97800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>110100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>114100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>111500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>117600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>136900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>136600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>135500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>148600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>154200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>230100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>235500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>247100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>399700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>426500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>468300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>451000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>408900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>209500</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>8</v>
       </c>
@@ -5923,8 +6109,11 @@
       <c r="AC76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6006,179 +6195,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-14500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-8900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-13900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-70400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-173900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1500</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
       <c r="U81" s="3">
+        <v>0</v>
+      </c>
+      <c r="V81" s="3">
         <v>-9900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>7100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6208,77 +6406,78 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E83" s="3">
         <v>1800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1700</v>
-      </c>
-      <c r="F83" s="3">
-        <v>1500</v>
       </c>
       <c r="G83" s="3">
         <v>1500</v>
       </c>
       <c r="H83" s="3">
-        <v>1700</v>
+        <v>1500</v>
       </c>
       <c r="I83" s="3">
         <v>1700</v>
       </c>
       <c r="J83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K83" s="3">
         <v>1800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>5400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4200</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X83" s="3">
+      <c r="X83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y83" s="3">
         <v>6800</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>8</v>
       </c>
@@ -6291,8 +6490,11 @@
       <c r="AC83" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6374,8 +6576,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6457,8 +6662,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6540,8 +6748,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6623,8 +6834,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6706,77 +6920,80 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E89" s="3">
         <v>1700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>11900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>7000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>15400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>10800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>10300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>11100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>12200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-8700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-14900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>13200</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X89" s="3">
+      <c r="X89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y89" s="3">
         <v>21700</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>8</v>
       </c>
@@ -6789,8 +7006,11 @@
       <c r="AC89" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6820,77 +7040,78 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-500</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-1800</v>
       </c>
       <c r="N91" s="3">
         <v>-1800</v>
       </c>
       <c r="O91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="P91" s="3">
         <v>-1900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-8200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2000</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X91" s="3">
+      <c r="X91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>8</v>
       </c>
@@ -6903,8 +7124,11 @@
       <c r="AC91" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6986,8 +7210,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7069,77 +7296,80 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-500</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-1800</v>
       </c>
       <c r="N94" s="3">
         <v>-1800</v>
       </c>
       <c r="O94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="P94" s="3">
         <v>-1900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-8200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-26300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-22700</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X94" s="3">
+      <c r="X94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>8</v>
       </c>
@@ -7152,8 +7382,11 @@
       <c r="AC94" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7183,8 +7416,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7224,8 +7458,8 @@
       <c r="O96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7266,8 +7500,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7349,8 +7586,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7432,8 +7672,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7515,77 +7758,80 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-11400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>7600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>4200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>8900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-14600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-14100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-12700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-11400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>13800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>22300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>8300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>30000</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X100" s="3">
+      <c r="X100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y100" s="3">
         <v>1200</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>8</v>
       </c>
@@ -7598,77 +7844,80 @@
       <c r="AC100" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1200</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-100</v>
       </c>
       <c r="J101" s="3">
         <v>-100</v>
       </c>
       <c r="K101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-400</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X101" s="3">
+      <c r="X101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y101" s="3">
         <v>700</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z101" s="3" t="s">
         <v>8</v>
       </c>
@@ -7681,77 +7930,80 @@
       <c r="AC101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-16100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>15300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-12900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-15600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>20100</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X102" s="3">
+      <c r="X102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y102" s="3">
         <v>21300</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>8</v>
       </c>
@@ -7762,6 +8014,9 @@
         <v>8</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>8</v>
       </c>
     </row>
